--- a/AAII_Financials/Quarterly/SOWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOWG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
   <si>
     <t>SOWG</t>
   </si>
@@ -656,130 +656,134 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
       <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
@@ -799,22 +803,25 @@
         <v>0</v>
       </c>
       <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
         <v>300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>200</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -822,31 +829,31 @@
         <v>2700</v>
       </c>
       <c r="E9" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
       <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>200</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
       <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
         <v>100</v>
       </c>
-      <c r="K9" s="3">
-        <v>0</v>
-      </c>
       <c r="L9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
+      <c r="M9" s="3">
+        <v>0</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
@@ -875,20 +882,23 @@
       <c r="V9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E10" s="3">
         <v>-1400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
       <c r="G10" s="3">
         <v>0</v>
       </c>
@@ -907,8 +917,8 @@
       <c r="L10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
+      <c r="M10" s="3">
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
@@ -937,8 +947,11 @@
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,8 +974,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1023,8 +1037,11 @@
       <c r="V12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,8 +1102,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1096,67 +1116,70 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>5200</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>1500</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-20400</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1180,7 +1203,7 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1209,8 +1232,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,61 +1256,62 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E17" s="3">
         <v>3800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1000</v>
-      </c>
-      <c r="P17" s="3">
-        <v>400</v>
       </c>
       <c r="Q17" s="3">
         <v>400</v>
       </c>
       <c r="R17" s="3">
+        <v>400</v>
+      </c>
+      <c r="S17" s="3">
         <v>-1000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-17200</v>
-      </c>
-      <c r="T17" s="3">
-        <v>400</v>
       </c>
       <c r="U17" s="3">
         <v>400</v>
@@ -1292,61 +1319,64 @@
       <c r="V17" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-400</v>
       </c>
       <c r="Q18" s="3">
         <v>-400</v>
       </c>
       <c r="R18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="S18" s="3">
         <v>1300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>17400</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-400</v>
       </c>
       <c r="U18" s="3">
         <v>-400</v>
@@ -1354,8 +1384,11 @@
       <c r="V18" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,8 +1411,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1408,93 +1442,96 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2000</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2800</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-1500</v>
       </c>
       <c r="L21" s="3">
         <v>-1500</v>
       </c>
       <c r="M21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="N21" s="3">
         <v>-800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>19500</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-400</v>
       </c>
       <c r="U21" s="3">
         <v>-400</v>
@@ -1502,19 +1539,22 @@
       <c r="V21" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
         <v>800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>500</v>
-      </c>
-      <c r="F22" s="3">
-        <v>400</v>
       </c>
       <c r="G22" s="3">
         <v>400</v>
@@ -1523,11 +1563,11 @@
         <v>400</v>
       </c>
       <c r="I22" s="3">
+        <v>400</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
@@ -1544,16 +1584,16 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>400</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1564,61 +1604,64 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2900</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-1600</v>
       </c>
       <c r="L23" s="3">
         <v>-1600</v>
       </c>
       <c r="M23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="N23" s="3">
         <v>-800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>19500</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-400</v>
       </c>
       <c r="U23" s="3">
         <v>-400</v>
@@ -1626,8 +1669,11 @@
       <c r="V23" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1688,8 +1734,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,61 +1799,64 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2900</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-1600</v>
       </c>
       <c r="L26" s="3">
         <v>-1600</v>
       </c>
       <c r="M26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="N26" s="3">
         <v>-800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>19500</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-400</v>
       </c>
       <c r="U26" s="3">
         <v>-400</v>
@@ -1812,61 +1864,64 @@
       <c r="V26" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2900</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-1600</v>
       </c>
       <c r="L27" s="3">
         <v>-1600</v>
       </c>
       <c r="M27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="N27" s="3">
         <v>-800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>19300</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-1000</v>
       </c>
       <c r="U27" s="3">
         <v>-1000</v>
@@ -1874,8 +1929,11 @@
       <c r="V27" s="3">
         <v>-1000</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1994,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1965,14 +2026,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>4</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -1987,19 +2048,22 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>-8200</v>
-      </c>
-      <c r="T29" s="3">
-        <v>300</v>
       </c>
       <c r="U29" s="3">
         <v>300</v>
       </c>
       <c r="V29" s="3">
+        <v>300</v>
+      </c>
+      <c r="W29" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2124,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,8 +2189,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2152,102 +2222,108 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2000</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2900</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-1600</v>
       </c>
       <c r="L33" s="3">
         <v>-1600</v>
       </c>
       <c r="M33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="N33" s="3">
         <v>-800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>11200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2384,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2900</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-1600</v>
       </c>
       <c r="L35" s="3">
         <v>-1600</v>
       </c>
       <c r="M35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="N35" s="3">
         <v>-800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>11200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2546,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,13 +2571,14 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>300</v>
+        <v>2100</v>
       </c>
       <c r="E41" s="3">
         <v>300</v>
@@ -2500,37 +2587,37 @@
         <v>300</v>
       </c>
       <c r="G41" s="3">
+        <v>300</v>
+      </c>
+      <c r="H41" s="3">
         <v>1400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>700</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>100</v>
       </c>
       <c r="R41" s="3">
         <v>100</v>
@@ -2539,16 +2626,19 @@
         <v>100</v>
       </c>
       <c r="T41" s="3">
+        <v>100</v>
+      </c>
+      <c r="U41" s="3">
         <v>300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2580,26 +2670,26 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5100</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R42" s="3">
+      <c r="R42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S42" s="3">
         <v>7000</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2609,19 +2699,22 @@
       <c r="V42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E43" s="3">
         <v>700</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
       <c r="F43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G43" s="3">
         <v>200</v>
@@ -2630,7 +2723,7 @@
         <v>200</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J43" s="3">
         <v>0</v>
@@ -2641,11 +2734,11 @@
       <c r="L43" s="3">
         <v>0</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2660,58 +2753,61 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E44" s="3">
         <v>900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1900</v>
-      </c>
-      <c r="H44" s="3">
-        <v>1800</v>
       </c>
       <c r="I44" s="3">
         <v>1800</v>
       </c>
       <c r="J44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K44" s="3">
         <v>1500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>100</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2727,14 +2823,17 @@
       <c r="T44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2763,16 +2862,16 @@
         <v>100</v>
       </c>
       <c r="L45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N45" s="3">
         <v>100</v>
       </c>
       <c r="O45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -2787,7 +2886,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U45" s="3">
         <v>100</v>
@@ -2795,79 +2894,85 @@
       <c r="V45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2100</v>
-      </c>
-      <c r="E46" s="3">
-        <v>2600</v>
       </c>
       <c r="F46" s="3">
         <v>2600</v>
       </c>
       <c r="G46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H46" s="3">
         <v>3600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
         <v>100</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
       <c r="F47" s="3">
         <v>0</v>
       </c>
@@ -2898,68 +3003,71 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R47" s="3">
         <v>4200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>14000</v>
-      </c>
-      <c r="T47" s="3">
-        <v>142000</v>
       </c>
       <c r="U47" s="3">
         <v>142000</v>
       </c>
       <c r="V47" s="3">
+        <v>142000</v>
+      </c>
+      <c r="W47" s="3">
         <v>141300</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E48" s="3">
         <v>6500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5800</v>
-      </c>
-      <c r="I48" s="3">
-        <v>4000</v>
       </c>
       <c r="J48" s="3">
         <v>4000</v>
       </c>
       <c r="K48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="L48" s="3">
         <v>4400</v>
-      </c>
-      <c r="L48" s="3">
-        <v>4200</v>
       </c>
       <c r="M48" s="3">
         <v>4200</v>
       </c>
       <c r="N48" s="3">
+        <v>4200</v>
+      </c>
+      <c r="O48" s="3">
         <v>3500</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
       <c r="P48" s="3">
         <v>0</v>
       </c>
@@ -2981,8 +3089,11 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2992,11 +3103,11 @@
       <c r="E49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
+      <c r="F49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G49" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
         <v>5200</v>
@@ -3008,7 +3119,7 @@
         <v>5200</v>
       </c>
       <c r="K49" s="3">
-        <v>6400</v>
+        <v>5200</v>
       </c>
       <c r="L49" s="3">
         <v>6400</v>
@@ -3019,8 +3130,8 @@
       <c r="N49" s="3">
         <v>6400</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
+      <c r="O49" s="3">
+        <v>6400</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>4</v>
@@ -3037,14 +3148,17 @@
       <c r="T49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3219,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,8 +3284,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3205,8 +3325,8 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
@@ -3223,14 +3343,17 @@
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,70 +3414,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E54" s="3">
         <v>8600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>142400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>143000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>142900</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3506,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,34 +3531,35 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
-      </c>
-      <c r="F57" s="3">
-        <v>500</v>
       </c>
       <c r="G57" s="3">
         <v>500</v>
       </c>
       <c r="H57" s="3">
+        <v>500</v>
+      </c>
+      <c r="I57" s="3">
         <v>1000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>300</v>
       </c>
       <c r="J57" s="3">
         <v>300</v>
       </c>
       <c r="K57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
@@ -3437,10 +3568,10 @@
         <v>200</v>
       </c>
       <c r="N57" s="3">
+        <v>200</v>
+      </c>
+      <c r="O57" s="3">
         <v>300</v>
-      </c>
-      <c r="O57" s="3">
-        <v>100</v>
       </c>
       <c r="P57" s="3">
         <v>100</v>
@@ -3449,31 +3580,34 @@
         <v>100</v>
       </c>
       <c r="R57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
       <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
         <v>200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>900</v>
+      </c>
+      <c r="E58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3489,8 +3623,8 @@
       <c r="J58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3504,14 +3638,14 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>4</v>
@@ -3525,40 +3659,43 @@
       <c r="V58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E59" s="3">
         <v>700</v>
-      </c>
-      <c r="E59" s="3">
-        <v>400</v>
       </c>
       <c r="F59" s="3">
         <v>400</v>
       </c>
       <c r="G59" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H59" s="3">
         <v>300</v>
       </c>
       <c r="I59" s="3">
+        <v>300</v>
+      </c>
+      <c r="J59" s="3">
         <v>200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>100</v>
-      </c>
-      <c r="K59" s="3">
-        <v>200</v>
       </c>
       <c r="L59" s="3">
         <v>200</v>
       </c>
       <c r="M59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N59" s="3">
         <v>300</v>
@@ -3567,51 +3704,54 @@
         <v>300</v>
       </c>
       <c r="P59" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q59" s="3">
         <v>1200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>500</v>
-      </c>
-      <c r="J60" s="3">
-        <v>400</v>
       </c>
       <c r="K60" s="3">
         <v>400</v>
@@ -3620,63 +3760,66 @@
         <v>400</v>
       </c>
       <c r="M60" s="3">
+        <v>400</v>
+      </c>
+      <c r="N60" s="3">
         <v>500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E61" s="3">
         <v>5100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1500</v>
-      </c>
-      <c r="K61" s="3">
-        <v>200</v>
       </c>
       <c r="L61" s="3">
         <v>200</v>
@@ -3685,7 +3828,7 @@
         <v>200</v>
       </c>
       <c r="N61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O61" s="3">
         <v>300</v>
@@ -3694,7 +3837,7 @@
         <v>300</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
@@ -3711,13 +3854,16 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="E62" s="3">
         <v>1300</v>
@@ -3735,7 +3881,7 @@
         <v>1300</v>
       </c>
       <c r="J62" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="K62" s="3">
         <v>1400</v>
@@ -3750,10 +3896,10 @@
         <v>1400</v>
       </c>
       <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
+        <v>1400</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
@@ -3764,8 +3910,8 @@
       <c r="S62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -3773,8 +3919,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3984,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4049,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,70 +4114,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E66" s="3">
         <v>7800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3300</v>
-      </c>
-      <c r="K66" s="3">
-        <v>1900</v>
       </c>
       <c r="L66" s="3">
         <v>1900</v>
       </c>
       <c r="M66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N66" s="3">
         <v>2000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>142200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>142100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>141400</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4206,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4269,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4334,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4399,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,70 +4464,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-60100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-60400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-57100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-55700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-48900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-47200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-45100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-43600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-40600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-39000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-37500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-36700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-35800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-33300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-34000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-31400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-27700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-36800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-36200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4594,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4659,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,70 +4724,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E76" s="3">
         <v>800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4854,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2900</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-1600</v>
       </c>
       <c r="L81" s="3">
         <v>-1600</v>
       </c>
       <c r="M81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="N81" s="3">
         <v>-800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>11200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,13 +5016,14 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
@@ -4851,7 +5050,7 @@
         <v>100</v>
       </c>
       <c r="M83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -4880,8 +5079,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5144,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5209,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5274,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5339,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5404,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1500</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-1000</v>
       </c>
       <c r="F89" s="3">
         <v>-1000</v>
       </c>
       <c r="G89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H89" s="3">
         <v>-1900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-400</v>
       </c>
       <c r="P89" s="3">
         <v>-400</v>
       </c>
       <c r="Q89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>-7600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1400</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-700</v>
       </c>
       <c r="V89" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,44 +5496,45 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>-1000</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
       </c>
       <c r="F91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
@@ -5323,8 +5544,8 @@
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -5335,11 +5556,14 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5624,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5689,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-200</v>
+        <v>-1000</v>
       </c>
       <c r="E94" s="3">
         <v>-200</v>
       </c>
       <c r="F94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G94" s="3">
         <v>-400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2000</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1000</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>6000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>100</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5781,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5610,8 +5844,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5909,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5974,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,43 +6039,46 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E100" s="3">
         <v>1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>800</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K100" s="3">
         <v>2100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>600</v>
-      </c>
-      <c r="L100" s="3">
-        <v>2500</v>
       </c>
       <c r="M100" s="3">
         <v>2500</v>
       </c>
       <c r="N100" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
@@ -5841,25 +6087,28 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>300</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>1400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5920,66 +6169,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-200</v>
-      </c>
-      <c r="T102" s="3">
-        <v>-600</v>
       </c>
       <c r="U102" s="3">
         <v>-600</v>
       </c>
       <c r="V102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="W102" s="3">
         <v>-600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOWG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>SOWG</t>
   </si>
@@ -656,140 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F8" s="3">
         <v>5000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>200</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
@@ -806,60 +813,66 @@
         <v>0</v>
       </c>
       <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
         <v>300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>200</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F9" s="3">
         <v>2700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2700</v>
-      </c>
-      <c r="F9" s="3">
-        <v>100</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
       </c>
       <c r="H9" s="3">
         <v>100</v>
       </c>
       <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>100</v>
+      </c>
+      <c r="K9" s="3">
         <v>200</v>
       </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
         <v>100</v>
       </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
+      <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>4</v>
@@ -885,26 +898,32 @@
       <c r="W9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F10" s="3">
         <v>2300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-1400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
       <c r="I10" s="3">
         <v>0</v>
       </c>
@@ -920,11 +939,11 @@
       <c r="M10" s="3">
         <v>0</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>4</v>
@@ -950,8 +969,14 @@
       <c r="W10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,8 +1000,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1040,8 +1067,14 @@
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,87 +1138,99 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>5200</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>1500</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-20400</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -1206,10 +1251,10 @@
         <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1235,8 +1280,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1308,152 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F17" s="3">
         <v>4700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>6400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1500</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1200</v>
       </c>
       <c r="P17" s="3">
         <v>1000</v>
       </c>
       <c r="Q17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>-1000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>-17200</v>
-      </c>
-      <c r="U17" s="3">
-        <v>400</v>
-      </c>
-      <c r="V17" s="3">
-        <v>400</v>
       </c>
       <c r="W17" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F18" s="3">
         <v>300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-6400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-2900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1500</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-1200</v>
       </c>
       <c r="P18" s="3">
         <v>-1000</v>
       </c>
       <c r="Q18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>17400</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-400</v>
       </c>
       <c r="W18" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,8 +1477,10 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1445,135 +1512,147 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>1500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-2200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-5000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>2000</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F21" s="3">
         <v>500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-2400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-6300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-2800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-2600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-3600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>19500</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-400</v>
       </c>
       <c r="W21" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E22" s="3">
+        <v>500</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>400</v>
-      </c>
-      <c r="H22" s="3">
-        <v>400</v>
       </c>
       <c r="I22" s="3">
         <v>400</v>
       </c>
       <c r="J22" s="3">
+        <v>400</v>
+      </c>
+      <c r="K22" s="3">
+        <v>400</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1587,19 +1666,19 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1607,73 +1686,85 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F23" s="3">
         <v>300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-6800</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-2100</v>
       </c>
       <c r="J23" s="3">
         <v>-1600</v>
       </c>
       <c r="K23" s="3">
-        <v>-2900</v>
+        <v>-2100</v>
       </c>
       <c r="L23" s="3">
         <v>-1600</v>
       </c>
       <c r="M23" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="N23" s="3">
         <v>-1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="P23" s="3">
         <v>-800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-3600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>19500</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-400</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-400</v>
       </c>
       <c r="W23" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1737,8 +1828,14 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1899,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F26" s="3">
         <v>300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-3300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-6800</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-2100</v>
       </c>
       <c r="J26" s="3">
         <v>-1600</v>
       </c>
       <c r="K26" s="3">
-        <v>-2900</v>
+        <v>-2100</v>
       </c>
       <c r="L26" s="3">
         <v>-1600</v>
       </c>
       <c r="M26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="N26" s="3">
         <v>-1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="P26" s="3">
         <v>-800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-2600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>19500</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-400</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-400</v>
       </c>
       <c r="W26" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F27" s="3">
         <v>300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-6800</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-2100</v>
       </c>
       <c r="J27" s="3">
         <v>-1600</v>
       </c>
       <c r="K27" s="3">
-        <v>-2900</v>
+        <v>-2100</v>
       </c>
       <c r="L27" s="3">
         <v>-1600</v>
       </c>
       <c r="M27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="N27" s="3">
         <v>-1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="P27" s="3">
         <v>-800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-2600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>19300</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-1000</v>
       </c>
       <c r="W27" s="3">
         <v>-1000</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2112,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2029,17 +2150,17 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2051,19 +2172,25 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-8200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>300</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>300</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2254,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,8 +2325,14 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2225,105 +2364,117 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>1500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-1500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>2200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>5000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-2000</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F33" s="3">
         <v>300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-6800</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-2100</v>
       </c>
       <c r="J33" s="3">
         <v>-1600</v>
       </c>
       <c r="K33" s="3">
-        <v>-2900</v>
+        <v>-2100</v>
       </c>
       <c r="L33" s="3">
         <v>-1600</v>
       </c>
       <c r="M33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="N33" s="3">
         <v>-1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="P33" s="3">
         <v>-800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>11200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2538,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F35" s="3">
         <v>300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-6800</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-2100</v>
       </c>
       <c r="J35" s="3">
         <v>-1600</v>
       </c>
       <c r="K35" s="3">
-        <v>-2900</v>
+        <v>-2100</v>
       </c>
       <c r="L35" s="3">
         <v>-1600</v>
       </c>
       <c r="M35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="N35" s="3">
         <v>-1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="P35" s="3">
         <v>-800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>11200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2716,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,73 +2743,81 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F41" s="3">
         <v>2100</v>
-      </c>
-      <c r="E41" s="3">
-        <v>300</v>
-      </c>
-      <c r="F41" s="3">
-        <v>300</v>
       </c>
       <c r="G41" s="3">
         <v>300</v>
       </c>
       <c r="H41" s="3">
+        <v>300</v>
+      </c>
+      <c r="I41" s="3">
+        <v>300</v>
+      </c>
+      <c r="J41" s="3">
         <v>1400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>700</v>
-      </c>
-      <c r="R41" s="3">
-        <v>100</v>
-      </c>
-      <c r="S41" s="3">
-        <v>100</v>
       </c>
       <c r="T41" s="3">
         <v>100</v>
       </c>
       <c r="U41" s="3">
+        <v>100</v>
+      </c>
+      <c r="V41" s="3">
+        <v>100</v>
+      </c>
+      <c r="W41" s="3">
         <v>300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2673,63 +2852,69 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>2200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>5100</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U42" s="3">
         <v>7000</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F43" s="3">
         <v>1400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>700</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>200</v>
-      </c>
       <c r="H43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I43" s="3">
         <v>200</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2737,14 +2922,14 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
+      <c r="N43" s="3">
+        <v>0</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2756,64 +2941,70 @@
         <v>0</v>
       </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2200</v>
+        <v>5100</v>
       </c>
       <c r="E44" s="3">
-        <v>900</v>
+        <v>4100</v>
       </c>
       <c r="F44" s="3">
         <v>2200</v>
       </c>
       <c r="G44" s="3">
+        <v>900</v>
+      </c>
+      <c r="H44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I44" s="3">
         <v>2000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>100</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2826,22 +3017,28 @@
       <c r="U44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
-      </c>
-      <c r="W44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>1300</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="F45" s="3">
         <v>100</v>
@@ -2865,19 +3062,19 @@
         <v>100</v>
       </c>
       <c r="M45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N45" s="3">
         <v>100</v>
       </c>
       <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -2889,96 +3086,108 @@
         <v>0</v>
       </c>
       <c r="U45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F46" s="3">
         <v>5900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3600</v>
-      </c>
-      <c r="I46" s="3">
-        <v>4900</v>
-      </c>
-      <c r="J46" s="3">
-        <v>3700</v>
       </c>
       <c r="K46" s="3">
         <v>4900</v>
       </c>
       <c r="L46" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M46" s="3">
+        <v>4900</v>
+      </c>
+      <c r="N46" s="3">
         <v>3800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>5700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>7100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E47" s="3">
+        <v>300</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
         <v>100</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
       <c r="H47" s="3">
         <v>0</v>
       </c>
@@ -3006,74 +3215,80 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
+      <c r="Q47" s="3">
+        <v>0</v>
       </c>
       <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T47" s="3">
         <v>4200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>7000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>14000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>142000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>142000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>141300</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F48" s="3">
         <v>7600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>6500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>6400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>6300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>6000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>5800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>4000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3500</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>0</v>
-      </c>
       <c r="R48" s="3">
         <v>0</v>
       </c>
@@ -3092,8 +3307,14 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3106,14 +3327,14 @@
       <c r="F49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>5200</v>
+      <c r="G49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I49" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>5200</v>
@@ -3122,10 +3343,10 @@
         <v>5200</v>
       </c>
       <c r="L49" s="3">
-        <v>6400</v>
+        <v>5200</v>
       </c>
       <c r="M49" s="3">
-        <v>6400</v>
+        <v>5200</v>
       </c>
       <c r="N49" s="3">
         <v>6400</v>
@@ -3133,11 +3354,11 @@
       <c r="O49" s="3">
         <v>6400</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>4</v>
+      <c r="P49" s="3">
+        <v>6400</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>6400</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>4</v>
@@ -3151,14 +3372,20 @@
       <c r="U49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
-      </c>
-      <c r="W49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3449,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,31 +3520,37 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
         <v>0</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3328,11 +3567,11 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>4</v>
@@ -3346,14 +3585,20 @@
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,73 +3662,85 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>21500</v>
+      </c>
+      <c r="F54" s="3">
         <v>13500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>8600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>9100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>8900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>14900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>16000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>12800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>14100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>14600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>15300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>14200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>12300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>5800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>4300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>7100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>14300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>142400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>143000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>142900</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3764,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,88 +3791,96 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>900</v>
+      </c>
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>300</v>
-      </c>
-      <c r="L57" s="3">
-        <v>200</v>
-      </c>
-      <c r="M57" s="3">
-        <v>200</v>
       </c>
       <c r="N57" s="3">
         <v>200</v>
       </c>
       <c r="O57" s="3">
+        <v>200</v>
+      </c>
+      <c r="P57" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q57" s="3">
         <v>300</v>
-      </c>
-      <c r="P57" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>100</v>
       </c>
       <c r="R57" s="3">
         <v>100</v>
       </c>
       <c r="S57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U57" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W57" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F58" s="3">
         <v>900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>300</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3626,11 +3893,11 @@
       <c r="K58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3641,8 +3908,8 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3650,8 +3917,8 @@
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>4</v>
@@ -3662,188 +3929,206 @@
       <c r="W58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F59" s="3">
         <v>1100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>300</v>
-      </c>
-      <c r="J59" s="3">
-        <v>200</v>
-      </c>
-      <c r="K59" s="3">
-        <v>100</v>
       </c>
       <c r="L59" s="3">
         <v>200</v>
       </c>
       <c r="M59" s="3">
+        <v>100</v>
+      </c>
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3">
-        <v>300</v>
-      </c>
       <c r="O59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P59" s="3">
         <v>300</v>
       </c>
       <c r="Q59" s="3">
+        <v>300</v>
+      </c>
+      <c r="R59" s="3">
+        <v>300</v>
+      </c>
+      <c r="S59" s="3">
         <v>1200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F60" s="3">
         <v>2700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1400</v>
-      </c>
-      <c r="F60" s="3">
-        <v>700</v>
-      </c>
-      <c r="G60" s="3">
-        <v>900</v>
       </c>
       <c r="H60" s="3">
         <v>700</v>
       </c>
       <c r="I60" s="3">
+        <v>900</v>
+      </c>
+      <c r="J60" s="3">
+        <v>700</v>
+      </c>
+      <c r="K60" s="3">
         <v>1400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>500</v>
-      </c>
-      <c r="K60" s="3">
-        <v>400</v>
-      </c>
-      <c r="L60" s="3">
-        <v>400</v>
       </c>
       <c r="M60" s="3">
         <v>400</v>
       </c>
       <c r="N60" s="3">
+        <v>400</v>
+      </c>
+      <c r="O60" s="3">
+        <v>400</v>
+      </c>
+      <c r="P60" s="3">
         <v>500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>2900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F61" s="3">
         <v>6400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>5100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>4600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>3900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>3500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1500</v>
-      </c>
-      <c r="L61" s="3">
-        <v>200</v>
-      </c>
-      <c r="M61" s="3">
-        <v>200</v>
       </c>
       <c r="N61" s="3">
         <v>200</v>
       </c>
       <c r="O61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q61" s="3">
         <v>300</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -3857,19 +4142,25 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F62" s="3">
         <v>1500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1300</v>
       </c>
       <c r="G62" s="3">
         <v>1300</v>
@@ -3884,10 +4175,10 @@
         <v>1300</v>
       </c>
       <c r="K62" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="L62" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="M62" s="3">
         <v>1400</v>
@@ -3899,13 +4190,13 @@
         <v>1400</v>
       </c>
       <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
+        <v>1400</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>4</v>
@@ -3913,17 +4204,23 @@
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4284,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4355,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,73 +4426,85 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>14200</v>
+      </c>
+      <c r="F66" s="3">
         <v>10600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>7800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>6100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>2900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>142200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>142100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>141400</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4528,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4595,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4666,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4402,8 +4737,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,73 +4808,85 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-58200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-58700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-60100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-60400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-57100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-55700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-48900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-47200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-45100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-43600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-40600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-39000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-37500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-36700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-35800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-33300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-34000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-31400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-27700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-36800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-36200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4950,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +5021,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,73 +5092,85 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F76" s="3">
         <v>2900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>9300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>10400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>9400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>10800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>12700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>13400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>12100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>10100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>3300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>5700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>11400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5234,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F81" s="3">
         <v>300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-6800</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-2100</v>
       </c>
       <c r="J81" s="3">
         <v>-1600</v>
       </c>
       <c r="K81" s="3">
-        <v>-2900</v>
+        <v>-2100</v>
       </c>
       <c r="L81" s="3">
         <v>-1600</v>
       </c>
       <c r="M81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="N81" s="3">
         <v>-1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="P81" s="3">
         <v>-800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>11200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,8 +5412,10 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5026,10 +5423,10 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -5053,10 +5450,10 @@
         <v>100</v>
       </c>
       <c r="N83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -5082,8 +5479,14 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5550,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5621,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5692,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5763,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,73 +5834,85 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-900</v>
+        <v>1300</v>
       </c>
       <c r="E89" s="3">
         <v>-1500</v>
       </c>
       <c r="F89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H89" s="3">
         <v>-1000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-800</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-1200</v>
       </c>
       <c r="L89" s="3">
         <v>-1500</v>
       </c>
       <c r="M89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="O89" s="3">
         <v>-1600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>-7600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,61 +5936,63 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-100</v>
-      </c>
       <c r="L91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
       </c>
       <c r="N91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -5559,11 +6000,17 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +6074,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,73 +6145,85 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-2000</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>2100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>1000</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>6000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>100</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6247,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5847,8 +6314,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6385,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6456,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,8 +6527,14 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6051,64 +6542,70 @@
         <v>3700</v>
       </c>
       <c r="E100" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F100" s="3">
+        <v>3700</v>
+      </c>
+      <c r="G100" s="3">
         <v>1600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>1300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>800</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3">
         <v>2100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>2500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>2500</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>300</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>1400</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6172,69 +6669,81 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>300</v>
+      </c>
+      <c r="F102" s="3">
         <v>1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOWG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
   <si>
     <t>SOWG</t>
   </si>
@@ -656,150 +656,154 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E8" s="3">
         <v>11400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
@@ -819,63 +823,66 @@
         <v>0</v>
       </c>
       <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
         <v>300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>200</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
       <c r="X8" s="3">
         <v>0</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E9" s="3">
         <v>6800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6100</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2700</v>
       </c>
       <c r="G9" s="3">
         <v>2700</v>
       </c>
       <c r="H9" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
       <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
         <v>100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>200</v>
       </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
       <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3">
         <v>100</v>
       </c>
-      <c r="N9" s="3">
-        <v>0</v>
-      </c>
       <c r="O9" s="3">
         <v>0</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
+      <c r="P9" s="3">
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>4</v>
@@ -904,29 +911,32 @@
       <c r="Y9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-1400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>100</v>
       </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
       <c r="J10" s="3">
         <v>0</v>
       </c>
@@ -945,8 +955,8 @@
       <c r="O10" s="3">
         <v>0</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
+      <c r="P10" s="3">
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
@@ -975,8 +985,11 @@
       <c r="Y10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1015,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1087,11 @@
       <c r="Y12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,19 +1161,22 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>700</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
@@ -1164,76 +1184,79 @@
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>5200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>1500</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-100</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-20400</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="3">
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
         <v>100</v>
@@ -1257,7 +1280,7 @@
         <v>100</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1286,8 +1309,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,70 +1336,71 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E17" s="3">
         <v>10500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1000</v>
-      </c>
-      <c r="S17" s="3">
-        <v>400</v>
       </c>
       <c r="T17" s="3">
         <v>400</v>
       </c>
       <c r="U17" s="3">
+        <v>400</v>
+      </c>
+      <c r="V17" s="3">
         <v>-1000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-17200</v>
-      </c>
-      <c r="W17" s="3">
-        <v>400</v>
       </c>
       <c r="X17" s="3">
         <v>400</v>
@@ -1381,70 +1408,73 @@
       <c r="Y17" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E18" s="3">
         <v>900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-6400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-400</v>
       </c>
       <c r="T18" s="3">
         <v>-400</v>
       </c>
       <c r="U18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V18" s="3">
         <v>1300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17400</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-400</v>
       </c>
       <c r="X18" s="3">
         <v>-400</v>
@@ -1452,8 +1482,11 @@
       <c r="Y18" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,13 +1512,14 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1518,102 +1552,105 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2000</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E21" s="3">
         <v>1100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-6300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2800</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-1500</v>
       </c>
       <c r="O21" s="3">
         <v>-1500</v>
       </c>
       <c r="P21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>19500</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-400</v>
       </c>
       <c r="X21" s="3">
         <v>-400</v>
@@ -1621,28 +1658,31 @@
       <c r="Y21" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>600</v>
+      </c>
+      <c r="E22" s="3">
         <v>400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>500</v>
-      </c>
-      <c r="I22" s="3">
-        <v>400</v>
       </c>
       <c r="J22" s="3">
         <v>400</v>
@@ -1651,11 +1691,11 @@
         <v>400</v>
       </c>
       <c r="L22" s="3">
+        <v>400</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1672,16 +1712,16 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1692,70 +1732,73 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E23" s="3">
         <v>500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2900</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-1600</v>
       </c>
       <c r="O23" s="3">
         <v>-1600</v>
       </c>
       <c r="P23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>19500</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-400</v>
       </c>
       <c r="X23" s="3">
         <v>-400</v>
@@ -1763,31 +1806,34 @@
       <c r="Y23" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1834,8 +1880,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,70 +1954,73 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E26" s="3">
         <v>500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2900</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-1600</v>
       </c>
       <c r="O26" s="3">
         <v>-1600</v>
       </c>
       <c r="P26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>19500</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-400</v>
       </c>
       <c r="X26" s="3">
         <v>-400</v>
@@ -1976,70 +2028,73 @@
       <c r="Y26" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E27" s="3">
         <v>500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2900</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-1600</v>
       </c>
       <c r="O27" s="3">
         <v>-1600</v>
       </c>
       <c r="P27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>19300</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-1000</v>
       </c>
       <c r="X27" s="3">
         <v>-1000</v>
@@ -2047,8 +2102,11 @@
       <c r="Y27" s="3">
         <v>-1000</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2156,14 +2217,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>4</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2178,19 +2239,22 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>-8200</v>
-      </c>
-      <c r="W29" s="3">
-        <v>300</v>
       </c>
       <c r="X29" s="3">
         <v>300</v>
       </c>
       <c r="Y29" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z29" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,13 +2398,16 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2370,111 +2440,117 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2000</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E33" s="3">
         <v>500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2900</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-1600</v>
       </c>
       <c r="O33" s="3">
         <v>-1600</v>
       </c>
       <c r="P33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>11200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E35" s="3">
         <v>500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2900</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-1600</v>
       </c>
       <c r="O35" s="3">
         <v>-1600</v>
       </c>
       <c r="P35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>11200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,22 +2831,23 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E41" s="3">
         <v>6800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2100</v>
-      </c>
-      <c r="G41" s="3">
-        <v>300</v>
       </c>
       <c r="H41" s="3">
         <v>300</v>
@@ -2769,37 +2856,37 @@
         <v>300</v>
       </c>
       <c r="J41" s="3">
+        <v>300</v>
+      </c>
+      <c r="K41" s="3">
         <v>1400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>700</v>
-      </c>
-      <c r="T41" s="3">
-        <v>100</v>
       </c>
       <c r="U41" s="3">
         <v>100</v>
@@ -2808,16 +2895,19 @@
         <v>100</v>
       </c>
       <c r="W41" s="3">
+        <v>100</v>
+      </c>
+      <c r="X41" s="3">
         <v>300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2858,26 +2948,26 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>5100</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U42" s="3">
+      <c r="U42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V42" s="3">
         <v>7000</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2887,28 +2977,31 @@
       <c r="Y42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E43" s="3">
         <v>2900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>700</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
       <c r="I43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J43" s="3">
         <v>200</v>
@@ -2917,7 +3010,7 @@
         <v>200</v>
       </c>
       <c r="L43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2928,11 +3021,11 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -2947,67 +3040,70 @@
         <v>0</v>
       </c>
       <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
         <v>200</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
       <c r="X43" s="3">
         <v>0</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E44" s="3">
         <v>5100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1900</v>
-      </c>
-      <c r="K44" s="3">
-        <v>1800</v>
       </c>
       <c r="L44" s="3">
         <v>1800</v>
       </c>
       <c r="M44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N44" s="3">
         <v>1500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>100</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3023,14 +3119,17 @@
       <c r="W44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
+      <c r="X44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3038,10 +3137,10 @@
         <v>1300</v>
       </c>
       <c r="E45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F45" s="3">
         <v>1100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>100</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
@@ -3068,16 +3167,16 @@
         <v>100</v>
       </c>
       <c r="O45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
       </c>
       <c r="R45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S45" s="3">
         <v>0</v>
@@ -3092,7 +3191,7 @@
         <v>0</v>
       </c>
       <c r="W45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X45" s="3">
         <v>100</v>
@@ -3100,97 +3199,103 @@
       <c r="Y45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E46" s="3">
         <v>16200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2100</v>
-      </c>
-      <c r="H46" s="3">
-        <v>2600</v>
       </c>
       <c r="I46" s="3">
         <v>2600</v>
       </c>
       <c r="J46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K46" s="3">
         <v>3600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E47" s="3">
         <v>400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>300</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
       <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
         <v>100</v>
       </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
       <c r="I47" s="3">
         <v>0</v>
       </c>
@@ -3221,77 +3326,80 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T47" s="3">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U47" s="3">
         <v>4200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>14000</v>
-      </c>
-      <c r="W47" s="3">
-        <v>142000</v>
       </c>
       <c r="X47" s="3">
         <v>142000</v>
       </c>
       <c r="Y47" s="3">
+        <v>142000</v>
+      </c>
+      <c r="Z47" s="3">
         <v>141300</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E48" s="3">
         <v>11300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5800</v>
-      </c>
-      <c r="L48" s="3">
-        <v>4000</v>
       </c>
       <c r="M48" s="3">
         <v>4000</v>
       </c>
       <c r="N48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="O48" s="3">
         <v>4400</v>
-      </c>
-      <c r="O48" s="3">
-        <v>4200</v>
       </c>
       <c r="P48" s="3">
         <v>4200</v>
       </c>
       <c r="Q48" s="3">
+        <v>4200</v>
+      </c>
+      <c r="R48" s="3">
         <v>3500</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
-      </c>
       <c r="S48" s="3">
         <v>0</v>
       </c>
@@ -3313,8 +3421,11 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3333,11 +3444,11 @@
       <c r="H49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
+      <c r="I49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J49" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>5200</v>
@@ -3349,7 +3460,7 @@
         <v>5200</v>
       </c>
       <c r="N49" s="3">
-        <v>6400</v>
+        <v>5200</v>
       </c>
       <c r="O49" s="3">
         <v>6400</v>
@@ -3360,8 +3471,8 @@
       <c r="Q49" s="3">
         <v>6400</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>4</v>
+      <c r="R49" s="3">
+        <v>6400</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>4</v>
@@ -3378,14 +3489,17 @@
       <c r="W49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,16 +3643,19 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>4</v>
@@ -3552,8 +3672,8 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -3573,8 +3693,8 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
+      <c r="R52" s="3">
+        <v>0</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>4</v>
@@ -3591,14 +3711,17 @@
       <c r="W52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3791,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E54" s="3">
         <v>27900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>142400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>143000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>142900</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,43 +3923,44 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="E57" s="3">
         <v>900</v>
       </c>
       <c r="F57" s="3">
+        <v>900</v>
+      </c>
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>500</v>
       </c>
       <c r="J57" s="3">
         <v>500</v>
       </c>
       <c r="K57" s="3">
+        <v>500</v>
+      </c>
+      <c r="L57" s="3">
         <v>1000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>300</v>
       </c>
       <c r="M57" s="3">
         <v>300</v>
       </c>
       <c r="N57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O57" s="3">
         <v>200</v>
@@ -3838,10 +3969,10 @@
         <v>200</v>
       </c>
       <c r="Q57" s="3">
+        <v>200</v>
+      </c>
+      <c r="R57" s="3">
         <v>300</v>
-      </c>
-      <c r="R57" s="3">
-        <v>100</v>
       </c>
       <c r="S57" s="3">
         <v>100</v>
@@ -3850,40 +3981,43 @@
         <v>100</v>
       </c>
       <c r="U57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
       </c>
       <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>800</v>
+      </c>
+      <c r="E58" s="3">
         <v>3000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3899,8 +4033,8 @@
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -3914,14 +4048,14 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>4</v>
@@ -3935,49 +4069,52 @@
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E59" s="3">
         <v>2700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>400</v>
       </c>
       <c r="I59" s="3">
         <v>400</v>
       </c>
       <c r="J59" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K59" s="3">
         <v>300</v>
       </c>
       <c r="L59" s="3">
+        <v>300</v>
+      </c>
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>100</v>
-      </c>
-      <c r="N59" s="3">
-        <v>200</v>
       </c>
       <c r="O59" s="3">
         <v>200</v>
       </c>
       <c r="P59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q59" s="3">
         <v>300</v>
@@ -3986,60 +4123,63 @@
         <v>300</v>
       </c>
       <c r="S59" s="3">
+        <v>300</v>
+      </c>
+      <c r="T59" s="3">
         <v>1200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E60" s="3">
         <v>6500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>500</v>
-      </c>
-      <c r="M60" s="3">
-        <v>400</v>
       </c>
       <c r="N60" s="3">
         <v>400</v>
@@ -4048,72 +4188,75 @@
         <v>400</v>
       </c>
       <c r="P60" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q60" s="3">
         <v>500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E61" s="3">
         <v>4900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1500</v>
-      </c>
-      <c r="N61" s="3">
-        <v>200</v>
       </c>
       <c r="O61" s="3">
         <v>200</v>
@@ -4122,7 +4265,7 @@
         <v>200</v>
       </c>
       <c r="Q61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R61" s="3">
         <v>300</v>
@@ -4131,7 +4274,7 @@
         <v>300</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
@@ -4148,22 +4291,25 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E62" s="3">
         <v>3500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1300</v>
       </c>
       <c r="H62" s="3">
         <v>1300</v>
@@ -4181,7 +4327,7 @@
         <v>1300</v>
       </c>
       <c r="M62" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="N62" s="3">
         <v>1400</v>
@@ -4196,10 +4342,10 @@
         <v>1400</v>
       </c>
       <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
+        <v>1400</v>
+      </c>
+      <c r="S62" s="3">
+        <v>0</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>4</v>
@@ -4210,8 +4356,8 @@
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4587,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E66" s="3">
         <v>15000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3300</v>
-      </c>
-      <c r="N66" s="3">
-        <v>1900</v>
       </c>
       <c r="O66" s="3">
         <v>1900</v>
       </c>
       <c r="P66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q66" s="3">
         <v>2000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>142200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>142100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>141400</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4985,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-54900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-58200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-58700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-60100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-60400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-57100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-55700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-48900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-47200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-45100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-43600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-40600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-39000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-37500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-36700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-35800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-33300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-34000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-31400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-27700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-36800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-36200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5281,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E76" s="3">
         <v>12900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E81" s="3">
         <v>500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2900</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-1600</v>
       </c>
       <c r="O81" s="3">
         <v>-1600</v>
       </c>
       <c r="P81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>11200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5612,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5429,7 +5628,7 @@
         <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -5456,7 +5655,7 @@
         <v>100</v>
       </c>
       <c r="P83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -5485,8 +5684,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6054,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E89" s="3">
         <v>1300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1500</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-1000</v>
       </c>
       <c r="I89" s="3">
         <v>-1000</v>
       </c>
       <c r="J89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K89" s="3">
         <v>-1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-600</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-400</v>
       </c>
       <c r="S89" s="3">
         <v>-400</v>
       </c>
       <c r="T89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>-7600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1400</v>
-      </c>
-      <c r="X89" s="3">
-        <v>-700</v>
       </c>
       <c r="Y89" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,53 +6158,54 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-200</v>
       </c>
       <c r="H91" s="3">
         <v>-200</v>
       </c>
       <c r="I91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-700</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
       </c>
@@ -5994,8 +6215,8 @@
       <c r="T91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -6006,11 +6227,14 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6378,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1000</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-200</v>
       </c>
       <c r="H94" s="3">
         <v>-200</v>
       </c>
       <c r="I94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J94" s="3">
         <v>-400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2000</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1000</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>6000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>100</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6482,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,52 +6776,55 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E100" s="3">
         <v>3700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>800</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N100" s="3">
         <v>2100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
-      </c>
-      <c r="O100" s="3">
-        <v>2500</v>
       </c>
       <c r="P100" s="3">
         <v>2500</v>
       </c>
       <c r="Q100" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
@@ -6587,25 +6833,28 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>300</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>1400</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6675,75 +6924,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E102" s="3">
         <v>4400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-100</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>-200</v>
-      </c>
-      <c r="W102" s="3">
-        <v>-600</v>
       </c>
       <c r="X102" s="3">
         <v>-600</v>
       </c>
       <c r="Y102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOWG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
   <si>
     <t>SOWG</t>
   </si>
@@ -656,157 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E8" s="3">
         <v>15600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
       <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>100</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
       <c r="P8" s="3">
         <v>0</v>
       </c>
@@ -826,66 +830,69 @@
         <v>0</v>
       </c>
       <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
         <v>300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>200</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
       <c r="Y8" s="3">
         <v>0</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E9" s="3">
         <v>6600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6800</v>
       </c>
-      <c r="F9" s="3">
-        <v>6100</v>
-      </c>
       <c r="G9" s="3">
-        <v>2700</v>
+        <v>6800</v>
       </c>
       <c r="H9" s="3">
-        <v>2700</v>
+        <v>3700</v>
       </c>
       <c r="I9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J9" s="3">
         <v>100</v>
       </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
       <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
         <v>100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>200</v>
       </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
       <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
         <v>100</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
       <c r="P9" s="3">
         <v>0</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>4</v>
+      <c r="Q9" s="3">
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>4</v>
@@ -914,32 +921,35 @@
       <c r="Z9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>600</v>
+      </c>
+      <c r="E10" s="3">
         <v>9000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4600</v>
       </c>
-      <c r="F10" s="3">
-        <v>3400</v>
-      </c>
       <c r="G10" s="3">
-        <v>2300</v>
+        <v>2700</v>
       </c>
       <c r="H10" s="3">
-        <v>-1400</v>
+        <v>1300</v>
       </c>
       <c r="I10" s="3">
+        <v>300</v>
+      </c>
+      <c r="J10" s="3">
         <v>100</v>
       </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
       <c r="K10" s="3">
         <v>0</v>
       </c>
@@ -958,8 +968,8 @@
       <c r="P10" s="3">
         <v>0</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
+      <c r="Q10" s="3">
+        <v>0</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>4</v>
@@ -988,8 +998,11 @@
       <c r="Z10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,8 +1029,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1090,8 +1104,11 @@
       <c r="Z12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,82 +1181,88 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
         <v>700</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-700</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="I14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>5200</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>1500</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-20400</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1249,17 +1272,17 @@
       <c r="E15" s="3">
         <v>0</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>4</v>
+      <c r="F15" s="3">
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
@@ -1283,7 +1306,7 @@
         <v>100</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1312,8 +1335,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,73 +1363,74 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>11500</v>
+        <v>6800</v>
       </c>
       <c r="E17" s="3">
+        <v>10800</v>
+      </c>
+      <c r="F17" s="3">
         <v>10500</v>
       </c>
-      <c r="F17" s="3">
-        <v>7700</v>
-      </c>
       <c r="G17" s="3">
+        <v>8400</v>
+      </c>
+      <c r="H17" s="3">
         <v>4700</v>
       </c>
-      <c r="H17" s="3">
-        <v>3800</v>
-      </c>
       <c r="I17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J17" s="3">
         <v>1100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1000</v>
-      </c>
-      <c r="T17" s="3">
-        <v>400</v>
       </c>
       <c r="U17" s="3">
         <v>400</v>
       </c>
       <c r="V17" s="3">
+        <v>400</v>
+      </c>
+      <c r="W17" s="3">
         <v>-1000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-17200</v>
-      </c>
-      <c r="X17" s="3">
-        <v>400</v>
       </c>
       <c r="Y17" s="3">
         <v>400</v>
@@ -1411,73 +1438,76 @@
       <c r="Z17" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4100</v>
+        <v>-3300</v>
       </c>
       <c r="E18" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F18" s="3">
         <v>900</v>
       </c>
-      <c r="F18" s="3">
-        <v>1800</v>
-      </c>
       <c r="G18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H18" s="3">
         <v>300</v>
       </c>
-      <c r="H18" s="3">
-        <v>-2500</v>
-      </c>
       <c r="I18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J18" s="3">
         <v>-900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-400</v>
       </c>
       <c r="U18" s="3">
         <v>-400</v>
       </c>
       <c r="V18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="W18" s="3">
         <v>1300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>17400</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-400</v>
       </c>
       <c r="Y18" s="3">
         <v>-400</v>
@@ -1485,8 +1515,11 @@
       <c r="Z18" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,31 +1546,32 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1555,105 +1589,108 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2000</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4400</v>
+        <v>-3200</v>
       </c>
       <c r="E21" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F21" s="3">
+        <v>900</v>
+      </c>
+      <c r="G21" s="3">
         <v>1100</v>
       </c>
-      <c r="F21" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>500</v>
-      </c>
       <c r="H21" s="3">
-        <v>-2400</v>
+        <v>300</v>
       </c>
       <c r="I21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2800</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-1500</v>
       </c>
       <c r="P21" s="3">
         <v>-1500</v>
       </c>
       <c r="Q21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="R21" s="3">
         <v>-800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>19500</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-400</v>
       </c>
       <c r="Y21" s="3">
         <v>-400</v>
@@ -1661,31 +1698,34 @@
       <c r="Z21" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
         <v>600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>500</v>
-      </c>
-      <c r="J22" s="3">
-        <v>400</v>
       </c>
       <c r="K22" s="3">
         <v>400</v>
@@ -1694,11 +1734,11 @@
         <v>400</v>
       </c>
       <c r="M22" s="3">
+        <v>400</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
@@ -1715,16 +1755,16 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>400</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1735,73 +1775,76 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E23" s="3">
         <v>3600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2900</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-1600</v>
       </c>
       <c r="P23" s="3">
         <v>-1600</v>
       </c>
       <c r="Q23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="R23" s="3">
         <v>-800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>19500</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-400</v>
       </c>
       <c r="Y23" s="3">
         <v>-400</v>
@@ -1809,17 +1852,20 @@
       <c r="Z23" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3" t="s">
         <v>4</v>
       </c>
@@ -1829,14 +1875,14 @@
       <c r="H24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1883,8 +1929,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,73 +2006,76 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E26" s="3">
         <v>3300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2900</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-1600</v>
       </c>
       <c r="P26" s="3">
         <v>-1600</v>
       </c>
       <c r="Q26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="R26" s="3">
         <v>-800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>19500</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-400</v>
       </c>
       <c r="Y26" s="3">
         <v>-400</v>
@@ -2031,73 +2083,76 @@
       <c r="Z26" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E27" s="3">
         <v>3300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2900</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-1600</v>
       </c>
       <c r="P27" s="3">
         <v>-1600</v>
       </c>
       <c r="Q27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="R27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>19300</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-1000</v>
       </c>
       <c r="Y27" s="3">
         <v>-1000</v>
@@ -2105,8 +2160,11 @@
       <c r="Z27" s="3">
         <v>-1000</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2220,14 +2281,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>4</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2242,19 +2303,22 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-8200</v>
-      </c>
-      <c r="X29" s="3">
-        <v>300</v>
       </c>
       <c r="Y29" s="3">
         <v>300</v>
       </c>
       <c r="Z29" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA29" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,31 +2468,34 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2443,114 +2513,120 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2000</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E33" s="3">
         <v>3300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2900</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-1600</v>
       </c>
       <c r="P33" s="3">
         <v>-1600</v>
       </c>
       <c r="Q33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="R33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>11200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2699,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E35" s="3">
         <v>3300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2900</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-1600</v>
       </c>
       <c r="P35" s="3">
         <v>-1600</v>
       </c>
       <c r="Q35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="R35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>11200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,25 +2918,26 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E41" s="3">
         <v>14400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2100</v>
-      </c>
-      <c r="H41" s="3">
-        <v>300</v>
       </c>
       <c r="I41" s="3">
         <v>300</v>
@@ -2859,37 +2946,37 @@
         <v>300</v>
       </c>
       <c r="K41" s="3">
+        <v>300</v>
+      </c>
+      <c r="L41" s="3">
         <v>1400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>700</v>
-      </c>
-      <c r="U41" s="3">
-        <v>100</v>
       </c>
       <c r="V41" s="3">
         <v>100</v>
@@ -2898,16 +2985,19 @@
         <v>100</v>
       </c>
       <c r="X41" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y41" s="3">
         <v>300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2951,26 +3041,26 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>5100</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V42" s="3">
+      <c r="V42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W42" s="3">
         <v>7000</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2980,31 +3070,34 @@
       <c r="Z42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E43" s="3">
         <v>6200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>700</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
       <c r="J43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K43" s="3">
         <v>200</v>
@@ -3013,7 +3106,7 @@
         <v>200</v>
       </c>
       <c r="M43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3024,11 +3117,11 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -3043,70 +3136,73 @@
         <v>0</v>
       </c>
       <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3">
         <v>200</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
-      </c>
       <c r="Y43" s="3">
         <v>0</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>10300</v>
+        <v>20000</v>
       </c>
       <c r="E44" s="3">
-        <v>5100</v>
+        <v>11500</v>
       </c>
       <c r="F44" s="3">
-        <v>4100</v>
+        <v>5900</v>
       </c>
       <c r="G44" s="3">
+        <v>4700</v>
+      </c>
+      <c r="H44" s="3">
         <v>2200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1900</v>
-      </c>
-      <c r="L44" s="3">
-        <v>1800</v>
       </c>
       <c r="M44" s="3">
         <v>1800</v>
       </c>
       <c r="N44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O44" s="3">
         <v>1500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>100</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3122,37 +3218,40 @@
       <c r="X44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
+      <c r="Y44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>100</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>100</v>
@@ -3170,16 +3269,16 @@
         <v>100</v>
       </c>
       <c r="P45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R45" s="3">
         <v>100</v>
       </c>
       <c r="S45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T45" s="3">
         <v>0</v>
@@ -3194,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="X45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3">
         <v>100</v>
@@ -3202,105 +3301,111 @@
       <c r="Z45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E46" s="3">
         <v>32200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2100</v>
-      </c>
-      <c r="I46" s="3">
-        <v>2600</v>
       </c>
       <c r="J46" s="3">
         <v>2600</v>
       </c>
       <c r="K46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="L46" s="3">
         <v>3600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>1400</v>
-      </c>
-      <c r="E47" s="3">
-        <v>400</v>
-      </c>
-      <c r="F47" s="3">
-        <v>300</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>100</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3329,80 +3434,83 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V47" s="3">
         <v>4200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>14000</v>
-      </c>
-      <c r="X47" s="3">
-        <v>142000</v>
       </c>
       <c r="Y47" s="3">
         <v>142000</v>
       </c>
       <c r="Z47" s="3">
+        <v>142000</v>
+      </c>
+      <c r="AA47" s="3">
         <v>141300</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E48" s="3">
         <v>26600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5800</v>
-      </c>
-      <c r="M48" s="3">
-        <v>4000</v>
       </c>
       <c r="N48" s="3">
         <v>4000</v>
       </c>
       <c r="O48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="P48" s="3">
         <v>4400</v>
-      </c>
-      <c r="P48" s="3">
-        <v>4200</v>
       </c>
       <c r="Q48" s="3">
         <v>4200</v>
       </c>
       <c r="R48" s="3">
+        <v>4200</v>
+      </c>
+      <c r="S48" s="3">
         <v>3500</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
       <c r="T48" s="3">
         <v>0</v>
       </c>
@@ -3424,34 +3532,37 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
       <c r="K49" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>5200</v>
@@ -3463,7 +3574,7 @@
         <v>5200</v>
       </c>
       <c r="O49" s="3">
-        <v>6400</v>
+        <v>5200</v>
       </c>
       <c r="P49" s="3">
         <v>6400</v>
@@ -3474,8 +3585,8 @@
       <c r="R49" s="3">
         <v>6400</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>4</v>
+      <c r="S49" s="3">
+        <v>6400</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>4</v>
@@ -3492,14 +3603,17 @@
       <c r="X49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,37 +3763,40 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3">
+        <v>1400</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
+        <v>1400</v>
+      </c>
+      <c r="F52" s="3">
+        <v>400</v>
+      </c>
+      <c r="G52" s="3">
+        <v>300</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>100</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -3696,8 +3816,8 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
+      <c r="S52" s="3">
+        <v>0</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>4</v>
@@ -3714,14 +3834,17 @@
       <c r="X52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3917,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>57700</v>
+      </c>
+      <c r="E54" s="3">
         <v>60200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>142400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>143000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>142900</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,46 +4054,47 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1800</v>
-      </c>
-      <c r="E57" s="3">
-        <v>900</v>
       </c>
       <c r="F57" s="3">
         <v>900</v>
       </c>
       <c r="G57" s="3">
+        <v>900</v>
+      </c>
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>300</v>
-      </c>
-      <c r="J57" s="3">
-        <v>500</v>
       </c>
       <c r="K57" s="3">
         <v>500</v>
       </c>
       <c r="L57" s="3">
+        <v>500</v>
+      </c>
+      <c r="M57" s="3">
         <v>1000</v>
-      </c>
-      <c r="M57" s="3">
-        <v>300</v>
       </c>
       <c r="N57" s="3">
         <v>300</v>
       </c>
       <c r="O57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
@@ -3972,10 +4103,10 @@
         <v>200</v>
       </c>
       <c r="R57" s="3">
+        <v>200</v>
+      </c>
+      <c r="S57" s="3">
         <v>300</v>
-      </c>
-      <c r="S57" s="3">
-        <v>100</v>
       </c>
       <c r="T57" s="3">
         <v>100</v>
@@ -3984,45 +4115,48 @@
         <v>100</v>
       </c>
       <c r="V57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
       </c>
       <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
         <v>200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>800</v>
+        <v>5100</v>
       </c>
       <c r="E58" s="3">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="F58" s="3">
-        <v>2900</v>
+        <v>3600</v>
       </c>
       <c r="G58" s="3">
-        <v>900</v>
+        <v>3400</v>
       </c>
       <c r="H58" s="3">
-        <v>300</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
+        <v>1100</v>
+      </c>
+      <c r="I58" s="3">
+        <v>400</v>
+      </c>
+      <c r="J58" s="3">
+        <v>100</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>4</v>
@@ -4036,8 +4170,8 @@
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -4051,14 +4185,14 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>4</v>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>4</v>
@@ -4072,52 +4206,55 @@
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3700</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
-        <v>2700</v>
-      </c>
-      <c r="F59" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H59" s="3">
-        <v>700</v>
-      </c>
-      <c r="I59" s="3">
+        <v>300</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>300</v>
       </c>
       <c r="L59" s="3">
         <v>300</v>
       </c>
       <c r="M59" s="3">
+        <v>300</v>
+      </c>
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>100</v>
-      </c>
-      <c r="O59" s="3">
-        <v>200</v>
       </c>
       <c r="P59" s="3">
         <v>200</v>
       </c>
       <c r="Q59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R59" s="3">
         <v>300</v>
@@ -4126,63 +4263,66 @@
         <v>300</v>
       </c>
       <c r="T59" s="3">
+        <v>300</v>
+      </c>
+      <c r="U59" s="3">
         <v>1200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E60" s="3">
         <v>6300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>500</v>
-      </c>
-      <c r="N60" s="3">
-        <v>400</v>
       </c>
       <c r="O60" s="3">
         <v>400</v>
@@ -4191,75 +4331,78 @@
         <v>400</v>
       </c>
       <c r="Q60" s="3">
+        <v>400</v>
+      </c>
+      <c r="R60" s="3">
         <v>500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2100</v>
+        <v>16200</v>
       </c>
       <c r="E61" s="3">
-        <v>4900</v>
+        <v>18900</v>
       </c>
       <c r="F61" s="3">
-        <v>4800</v>
+        <v>8500</v>
       </c>
       <c r="G61" s="3">
+        <v>8400</v>
+      </c>
+      <c r="H61" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I61" s="3">
         <v>6400</v>
       </c>
-      <c r="H61" s="3">
-        <v>5100</v>
-      </c>
-      <c r="I61" s="3">
-        <v>4600</v>
-      </c>
       <c r="J61" s="3">
+        <v>5900</v>
+      </c>
+      <c r="K61" s="3">
         <v>3900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1500</v>
-      </c>
-      <c r="O61" s="3">
-        <v>200</v>
       </c>
       <c r="P61" s="3">
         <v>200</v>
@@ -4268,7 +4411,7 @@
         <v>200</v>
       </c>
       <c r="R61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="S61" s="3">
         <v>300</v>
@@ -4277,7 +4420,7 @@
         <v>300</v>
       </c>
       <c r="U61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
@@ -4294,31 +4437,34 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>16800</v>
-      </c>
-      <c r="E62" s="3">
-        <v>3500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>3700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J62" s="3">
-        <v>1300</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K62" s="3">
         <v>1300</v>
@@ -4330,7 +4476,7 @@
         <v>1300</v>
       </c>
       <c r="N62" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="O62" s="3">
         <v>1400</v>
@@ -4345,10 +4491,10 @@
         <v>1400</v>
       </c>
       <c r="S62" s="3">
-        <v>0</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
+        <v>1400</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>4</v>
@@ -4359,8 +4505,8 @@
       <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
@@ -4368,8 +4514,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,82 +4745,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E66" s="3">
         <v>25200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>15000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3300</v>
-      </c>
-      <c r="O66" s="3">
-        <v>1900</v>
       </c>
       <c r="P66" s="3">
         <v>1900</v>
       </c>
       <c r="Q66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R66" s="3">
         <v>2000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>142200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>142100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>141400</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5159,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-58300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-54900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-58200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-58700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-60100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-60400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-57100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-55700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-48900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-47200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-45100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-43600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-40600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-39000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-37500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-36700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-35800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-33300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-34000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-31400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-27700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-36800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-36200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5467,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E76" s="3">
         <v>35000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5621,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E81" s="3">
         <v>3300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2900</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-1600</v>
       </c>
       <c r="P81" s="3">
         <v>-1600</v>
       </c>
       <c r="Q81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="R81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>11200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,8 +5811,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5622,13 +5821,13 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -5658,7 +5857,7 @@
         <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -5687,8 +5886,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6271,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1500</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-1000</v>
       </c>
       <c r="J89" s="3">
         <v>-1000</v>
       </c>
       <c r="K89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="L89" s="3">
         <v>-1900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-600</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-400</v>
       </c>
       <c r="T89" s="3">
         <v>-400</v>
       </c>
       <c r="U89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V89" s="3">
         <v>-300</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>-7600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1400</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-700</v>
       </c>
       <c r="Z89" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,56 +6379,57 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-200</v>
       </c>
       <c r="I91" s="3">
         <v>-200</v>
       </c>
       <c r="J91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-700</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>4</v>
       </c>
@@ -6218,8 +6439,8 @@
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -6230,11 +6451,14 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,82 +6608,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1000</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-200</v>
       </c>
       <c r="I94" s="3">
         <v>-200</v>
       </c>
       <c r="J94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2000</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1000</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>6000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>100</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,31 +6716,32 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6557,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,55 +7022,58 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>11400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O100" s="3">
         <v>2100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>600</v>
-      </c>
-      <c r="P100" s="3">
-        <v>2500</v>
       </c>
       <c r="Q100" s="3">
         <v>2500</v>
       </c>
       <c r="R100" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="S100" s="3">
         <v>0</v>
@@ -6836,48 +7082,51 @@
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>300</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>1400</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6927,78 +7176,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E102" s="3">
         <v>7600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>-200</v>
-      </c>
-      <c r="X102" s="3">
-        <v>-600</v>
       </c>
       <c r="Y102" s="3">
         <v>-600</v>
       </c>
       <c r="Z102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOWG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
   <si>
     <t>SOWG</t>
   </si>
@@ -656,164 +656,167 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E8" s="3">
         <v>3600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>200</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
       <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
         <v>100</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
@@ -833,69 +836,72 @@
         <v>0</v>
       </c>
       <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
         <v>300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>200</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
-      </c>
       <c r="Z8" s="3">
         <v>0</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E9" s="3">
         <v>3000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6600</v>
-      </c>
-      <c r="F9" s="3">
-        <v>6800</v>
       </c>
       <c r="G9" s="3">
         <v>6800</v>
       </c>
       <c r="H9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="I9" s="3">
         <v>3700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>100</v>
       </c>
-      <c r="K9" s="3">
-        <v>0</v>
-      </c>
       <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
         <v>100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>200</v>
       </c>
-      <c r="N9" s="3">
-        <v>0</v>
-      </c>
       <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
         <v>100</v>
       </c>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
       <c r="Q9" s="3">
         <v>0</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>4</v>
+      <c r="R9" s="3">
+        <v>0</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>4</v>
@@ -924,35 +930,38 @@
       <c r="AA9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E10" s="3">
         <v>600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
       <c r="L10" s="3">
         <v>0</v>
       </c>
@@ -971,8 +980,8 @@
       <c r="Q10" s="3">
         <v>0</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>4</v>
+      <c r="R10" s="3">
+        <v>0</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>4</v>
@@ -1001,8 +1010,11 @@
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1107,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,85 +1200,91 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>700</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>-700</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>1900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>5200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>1500</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-100</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-20400</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1276,16 +1298,16 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
         <v>-100</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
@@ -1309,7 +1331,7 @@
         <v>100</v>
       </c>
       <c r="R15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1338,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,76 +1389,77 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E17" s="3">
         <v>6800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1000</v>
-      </c>
-      <c r="U17" s="3">
-        <v>400</v>
       </c>
       <c r="V17" s="3">
         <v>400</v>
       </c>
       <c r="W17" s="3">
+        <v>400</v>
+      </c>
+      <c r="X17" s="3">
         <v>-1000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>-17200</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>400</v>
       </c>
       <c r="Z17" s="3">
         <v>400</v>
@@ -1441,76 +1467,79 @@
       <c r="AA17" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-400</v>
       </c>
       <c r="V18" s="3">
         <v>-400</v>
       </c>
       <c r="W18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="X18" s="3">
         <v>1300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>17400</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-400</v>
       </c>
       <c r="Z18" s="3">
         <v>-400</v>
@@ -1518,8 +1547,11 @@
       <c r="AA18" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,8 +1579,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1573,8 +1606,8 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1592,108 +1625,111 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2000</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2800</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-1500</v>
       </c>
       <c r="Q21" s="3">
         <v>-1500</v>
       </c>
       <c r="R21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="S21" s="3">
         <v>-800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>19500</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-400</v>
       </c>
       <c r="Z21" s="3">
         <v>-400</v>
@@ -1701,8 +1737,11 @@
       <c r="AA21" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1710,25 +1749,25 @@
         <v>200</v>
       </c>
       <c r="E22" s="3">
+        <v>200</v>
+      </c>
+      <c r="F22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>500</v>
-      </c>
-      <c r="K22" s="3">
-        <v>400</v>
       </c>
       <c r="L22" s="3">
         <v>400</v>
@@ -1737,11 +1776,11 @@
         <v>400</v>
       </c>
       <c r="N22" s="3">
+        <v>400</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -1758,16 +1797,16 @@
         <v>0</v>
       </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>400</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -1778,76 +1817,79 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2900</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-1600</v>
       </c>
       <c r="Q23" s="3">
         <v>-1600</v>
       </c>
       <c r="R23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="S23" s="3">
         <v>-800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>19500</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-400</v>
       </c>
       <c r="Z23" s="3">
         <v>-400</v>
@@ -1855,8 +1897,11 @@
       <c r="AA23" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1864,11 +1909,11 @@
         <v>-100</v>
       </c>
       <c r="E24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>4</v>
       </c>
@@ -1884,8 +1929,8 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1932,8 +1977,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,76 +2057,79 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2900</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-1600</v>
       </c>
       <c r="Q26" s="3">
         <v>-1600</v>
       </c>
       <c r="R26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="S26" s="3">
         <v>-800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>19500</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-400</v>
       </c>
       <c r="Z26" s="3">
         <v>-400</v>
@@ -2086,76 +2137,79 @@
       <c r="AA26" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2900</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-1600</v>
       </c>
       <c r="Q27" s="3">
         <v>-1600</v>
       </c>
       <c r="R27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="S27" s="3">
         <v>-800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>19300</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-1000</v>
       </c>
       <c r="Z27" s="3">
         <v>-1000</v>
@@ -2163,8 +2217,11 @@
       <c r="AA27" s="3">
         <v>-1000</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2284,14 +2344,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>4</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2306,19 +2366,22 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-8200</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>300</v>
       </c>
       <c r="Z29" s="3">
         <v>300</v>
       </c>
       <c r="AA29" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB29" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,8 +2537,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2497,8 +2566,8 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -2516,117 +2585,123 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2900</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-1600</v>
       </c>
       <c r="Q33" s="3">
         <v>-1600</v>
       </c>
       <c r="R33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>11200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2900</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-1600</v>
       </c>
       <c r="Q35" s="3">
         <v>-1600</v>
       </c>
       <c r="R35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>11200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,28 +3004,29 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E41" s="3">
         <v>6900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2100</v>
-      </c>
-      <c r="I41" s="3">
-        <v>300</v>
       </c>
       <c r="J41" s="3">
         <v>300</v>
@@ -2949,37 +3035,37 @@
         <v>300</v>
       </c>
       <c r="L41" s="3">
+        <v>300</v>
+      </c>
+      <c r="M41" s="3">
         <v>1400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>700</v>
-      </c>
-      <c r="V41" s="3">
-        <v>100</v>
       </c>
       <c r="W41" s="3">
         <v>100</v>
@@ -2988,16 +3074,19 @@
         <v>100</v>
       </c>
       <c r="Y41" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z41" s="3">
         <v>300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3044,26 +3133,26 @@
         <v>0</v>
       </c>
       <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
         <v>500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>5100</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W42" s="3">
+      <c r="W42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X42" s="3">
         <v>7000</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3073,34 +3162,37 @@
       <c r="AA42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>700</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
       <c r="K43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3">
         <v>200</v>
@@ -3109,7 +3201,7 @@
         <v>200</v>
       </c>
       <c r="N43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -3120,11 +3212,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -3139,73 +3231,76 @@
         <v>0</v>
       </c>
       <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
         <v>200</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
-      </c>
       <c r="Z43" s="3">
         <v>0</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E44" s="3">
         <v>20000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>11500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1900</v>
-      </c>
-      <c r="M44" s="3">
-        <v>1800</v>
       </c>
       <c r="N44" s="3">
         <v>1800</v>
       </c>
       <c r="O44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P44" s="3">
         <v>1500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>100</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3221,14 +3316,17 @@
       <c r="Y44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z44" s="3">
-        <v>0</v>
+      <c r="Z44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3253,8 +3351,8 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
-        <v>100</v>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L45" s="3">
         <v>100</v>
@@ -3272,16 +3370,16 @@
         <v>100</v>
       </c>
       <c r="Q45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S45" s="3">
         <v>100</v>
       </c>
       <c r="T45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
@@ -3296,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="Y45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="3">
         <v>100</v>
@@ -3304,85 +3402,91 @@
       <c r="AA45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E46" s="3">
         <v>28400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>32200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2100</v>
-      </c>
-      <c r="J46" s="3">
-        <v>2600</v>
       </c>
       <c r="K46" s="3">
         <v>2600</v>
       </c>
       <c r="L46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M46" s="3">
         <v>3600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3407,8 +3511,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3437,83 +3541,86 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W47" s="3">
         <v>4200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>14000</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>142000</v>
       </c>
       <c r="Z47" s="3">
         <v>142000</v>
       </c>
       <c r="AA47" s="3">
+        <v>142000</v>
+      </c>
+      <c r="AB47" s="3">
         <v>141300</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E48" s="3">
         <v>27900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5800</v>
-      </c>
-      <c r="N48" s="3">
-        <v>4000</v>
       </c>
       <c r="O48" s="3">
         <v>4000</v>
       </c>
       <c r="P48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Q48" s="3">
         <v>4400</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>4200</v>
       </c>
       <c r="R48" s="3">
         <v>4200</v>
       </c>
       <c r="S48" s="3">
+        <v>4200</v>
+      </c>
+      <c r="T48" s="3">
         <v>3500</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
-      </c>
       <c r="U48" s="3">
         <v>0</v>
       </c>
@@ -3535,8 +3642,11 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3565,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="L49" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="M49" s="3">
         <v>5200</v>
@@ -3577,7 +3687,7 @@
         <v>5200</v>
       </c>
       <c r="P49" s="3">
-        <v>6400</v>
+        <v>5200</v>
       </c>
       <c r="Q49" s="3">
         <v>6400</v>
@@ -3588,8 +3698,8 @@
       <c r="S49" s="3">
         <v>6400</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>4</v>
+      <c r="T49" s="3">
+        <v>6400</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>4</v>
@@ -3606,14 +3716,17 @@
       <c r="Y49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,8 +3882,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3778,28 +3897,28 @@
         <v>1400</v>
       </c>
       <c r="F52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G52" s="3">
         <v>400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>300</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -3819,8 +3938,8 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
+      <c r="T52" s="3">
+        <v>0</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>4</v>
@@ -3837,14 +3956,17 @@
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,85 +4042,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>54700</v>
+      </c>
+      <c r="E54" s="3">
         <v>57700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>60200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>14300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>142400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>143000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>142900</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,49 +4184,50 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1800</v>
-      </c>
-      <c r="F57" s="3">
-        <v>900</v>
       </c>
       <c r="G57" s="3">
         <v>900</v>
       </c>
       <c r="H57" s="3">
+        <v>900</v>
+      </c>
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>300</v>
-      </c>
-      <c r="K57" s="3">
-        <v>500</v>
       </c>
       <c r="L57" s="3">
         <v>500</v>
       </c>
       <c r="M57" s="3">
+        <v>500</v>
+      </c>
+      <c r="N57" s="3">
         <v>1000</v>
-      </c>
-      <c r="N57" s="3">
-        <v>300</v>
       </c>
       <c r="O57" s="3">
         <v>300</v>
       </c>
       <c r="P57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q57" s="3">
         <v>200</v>
@@ -4106,10 +4236,10 @@
         <v>200</v>
       </c>
       <c r="S57" s="3">
+        <v>200</v>
+      </c>
+      <c r="T57" s="3">
         <v>300</v>
-      </c>
-      <c r="T57" s="3">
-        <v>100</v>
       </c>
       <c r="U57" s="3">
         <v>100</v>
@@ -4118,49 +4248,52 @@
         <v>100</v>
       </c>
       <c r="W57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X57" s="3">
         <v>0</v>
       </c>
       <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3">
         <v>200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E58" s="3">
         <v>5100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4173,8 +4306,8 @@
       <c r="O58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4188,14 +4321,14 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>4</v>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>4</v>
@@ -4209,20 +4342,23 @@
       <c r="AA58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3">
         <v>100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>300</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4235,29 +4371,29 @@
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>300</v>
       </c>
       <c r="M59" s="3">
         <v>300</v>
       </c>
       <c r="N59" s="3">
+        <v>300</v>
+      </c>
+      <c r="O59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>100</v>
-      </c>
-      <c r="P59" s="3">
-        <v>200</v>
       </c>
       <c r="Q59" s="3">
         <v>200</v>
       </c>
       <c r="R59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="S59" s="3">
         <v>300</v>
@@ -4266,66 +4402,69 @@
         <v>300</v>
       </c>
       <c r="U59" s="3">
+        <v>300</v>
+      </c>
+      <c r="V59" s="3">
         <v>1200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E60" s="3">
         <v>8700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>500</v>
-      </c>
-      <c r="O60" s="3">
-        <v>400</v>
       </c>
       <c r="P60" s="3">
         <v>400</v>
@@ -4334,78 +4473,81 @@
         <v>400</v>
       </c>
       <c r="R60" s="3">
+        <v>400</v>
+      </c>
+      <c r="S60" s="3">
         <v>500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E61" s="3">
         <v>16200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1500</v>
-      </c>
-      <c r="P61" s="3">
-        <v>200</v>
       </c>
       <c r="Q61" s="3">
         <v>200</v>
@@ -4414,7 +4556,7 @@
         <v>200</v>
       </c>
       <c r="S61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="T61" s="3">
         <v>300</v>
@@ -4423,7 +4565,7 @@
         <v>300</v>
       </c>
       <c r="V61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
@@ -4440,8 +4582,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4466,8 +4611,8 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
-        <v>1300</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L62" s="3">
         <v>1300</v>
@@ -4479,7 +4624,7 @@
         <v>1300</v>
       </c>
       <c r="O62" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="P62" s="3">
         <v>1400</v>
@@ -4494,10 +4639,10 @@
         <v>1400</v>
       </c>
       <c r="T62" s="3">
-        <v>0</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
+        <v>1400</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>4</v>
@@ -4508,8 +4653,8 @@
       <c r="X62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
@@ -4517,8 +4662,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,85 +4902,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E66" s="3">
         <v>24800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>15000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3300</v>
-      </c>
-      <c r="P66" s="3">
-        <v>1900</v>
       </c>
       <c r="Q66" s="3">
         <v>1900</v>
       </c>
       <c r="R66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="S66" s="3">
         <v>2000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>142200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>142100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>141400</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5085,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,85 +5332,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-62400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-58300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-54900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-58200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-58700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-60100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-60400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-57100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-55700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-48900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-47200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-45100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-43600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-40600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-39000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-37500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-36700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-35800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-33300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-34000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-31400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-27700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-36800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-36200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E76" s="3">
         <v>32800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>35000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2900</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-1600</v>
       </c>
       <c r="Q81" s="3">
         <v>-1600</v>
       </c>
       <c r="R81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>11200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,8 +6009,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5821,7 +6019,7 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -5860,7 +6058,7 @@
         <v>100</v>
       </c>
       <c r="R83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -5889,8 +6087,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1500</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-1000</v>
       </c>
       <c r="K89" s="3">
         <v>-1000</v>
       </c>
       <c r="L89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M89" s="3">
         <v>-1900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-600</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-400</v>
       </c>
       <c r="U89" s="3">
         <v>-400</v>
       </c>
       <c r="V89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="W89" s="3">
         <v>-300</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1400</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-700</v>
       </c>
       <c r="AA89" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,59 +6599,60 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-200</v>
       </c>
       <c r="J91" s="3">
         <v>-200</v>
       </c>
       <c r="K91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>4</v>
       </c>
@@ -6442,8 +6662,8 @@
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -6454,11 +6674,14 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1000</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-200</v>
       </c>
       <c r="J94" s="3">
         <v>-200</v>
       </c>
       <c r="K94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2000</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1000</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>6000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>100</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6743,8 +6976,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6794,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,58 +7267,61 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>11400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>800</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P100" s="3">
         <v>2100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>600</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>2500</v>
       </c>
       <c r="R100" s="3">
         <v>2500</v>
       </c>
       <c r="S100" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
@@ -7085,25 +7330,28 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>300</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>1400</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7128,8 +7376,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7179,81 +7427,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>-600</v>
       </c>
       <c r="Z102" s="3">
         <v>-600</v>
       </c>
       <c r="AA102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOWG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
   <si>
     <t>SOWG</t>
   </si>
@@ -656,170 +656,174 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
       <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
         <v>100</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
@@ -839,72 +843,75 @@
         <v>0</v>
       </c>
       <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
         <v>300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>200</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
-      </c>
       <c r="AA8" s="3">
         <v>0</v>
       </c>
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E9" s="3">
         <v>2600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6600</v>
-      </c>
-      <c r="G9" s="3">
-        <v>6800</v>
       </c>
       <c r="H9" s="3">
         <v>6800</v>
       </c>
       <c r="I9" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J9" s="3">
         <v>3700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>100</v>
       </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
       <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3">
         <v>100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>200</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
       <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
         <v>100</v>
       </c>
-      <c r="Q9" s="3">
-        <v>0</v>
-      </c>
       <c r="R9" s="3">
         <v>0</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>4</v>
+      <c r="S9" s="3">
+        <v>0</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>4</v>
@@ -933,38 +940,41 @@
       <c r="AB9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-1200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4600</v>
       </c>
-      <c r="H10" s="3">
-        <v>2700</v>
-      </c>
       <c r="I10" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J10" s="3">
         <v>1300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3">
-        <v>0</v>
-      </c>
       <c r="M10" s="3">
         <v>0</v>
       </c>
@@ -983,8 +993,8 @@
       <c r="R10" s="3">
         <v>0</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>4</v>
+      <c r="S10" s="3">
+        <v>0</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>4</v>
@@ -1013,8 +1023,11 @@
       <c r="AB10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,8 +1056,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1123,8 +1137,11 @@
       <c r="AB12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,88 +1220,94 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>700</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>1900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>5200</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1500</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-100</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-20400</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1301,7 +1324,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -1310,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>100</v>
@@ -1334,7 +1357,7 @@
         <v>100</v>
       </c>
       <c r="S15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,79 +1416,80 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E17" s="3">
         <v>5500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10500</v>
       </c>
-      <c r="H17" s="3">
-        <v>8400</v>
-      </c>
       <c r="I17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="J17" s="3">
         <v>4700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1000</v>
-      </c>
-      <c r="V17" s="3">
-        <v>400</v>
       </c>
       <c r="W17" s="3">
         <v>400</v>
       </c>
       <c r="X17" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y17" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>-17200</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>400</v>
       </c>
       <c r="AA17" s="3">
         <v>400</v>
@@ -1470,79 +1497,82 @@
       <c r="AB17" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>900</v>
       </c>
-      <c r="H18" s="3">
-        <v>1100</v>
-      </c>
       <c r="I18" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J18" s="3">
         <v>300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-400</v>
       </c>
       <c r="W18" s="3">
         <v>-400</v>
       </c>
       <c r="X18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y18" s="3">
         <v>1300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>17400</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-400</v>
       </c>
       <c r="AA18" s="3">
         <v>-400</v>
@@ -1550,8 +1580,11 @@
       <c r="AB18" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,8 +1613,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1609,8 +1643,8 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1628,111 +1662,114 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2000</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>900</v>
       </c>
-      <c r="H21" s="3">
-        <v>1100</v>
-      </c>
       <c r="I21" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J21" s="3">
         <v>300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2800</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-1500</v>
       </c>
       <c r="R21" s="3">
         <v>-1500</v>
       </c>
       <c r="S21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="T21" s="3">
         <v>-800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>19500</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>-400</v>
       </c>
       <c r="AA21" s="3">
         <v>-400</v>
@@ -1740,8 +1777,11 @@
       <c r="AB21" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1752,25 +1792,25 @@
         <v>200</v>
       </c>
       <c r="F22" s="3">
+        <v>200</v>
+      </c>
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>500</v>
-      </c>
-      <c r="L22" s="3">
-        <v>400</v>
       </c>
       <c r="M22" s="3">
         <v>400</v>
@@ -1779,11 +1819,11 @@
         <v>400</v>
       </c>
       <c r="O22" s="3">
+        <v>400</v>
+      </c>
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -1800,16 +1840,16 @@
         <v>0</v>
       </c>
       <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>400</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -1820,79 +1860,82 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-1600</v>
       </c>
       <c r="R23" s="3">
         <v>-1600</v>
       </c>
       <c r="S23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="T23" s="3">
         <v>-800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>19500</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-400</v>
       </c>
       <c r="AA23" s="3">
         <v>-400</v>
@@ -1900,23 +1943,26 @@
       <c r="AB23" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>-100</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E24" s="3">
         <v>-100</v>
       </c>
       <c r="F24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H24" s="3" t="s">
         <v>4</v>
       </c>
@@ -1932,8 +1978,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1980,8 +2026,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,79 +2109,82 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-1600</v>
       </c>
       <c r="R26" s="3">
         <v>-1600</v>
       </c>
       <c r="S26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="T26" s="3">
         <v>-800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>19500</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-400</v>
       </c>
       <c r="AA26" s="3">
         <v>-400</v>
@@ -2140,79 +2192,82 @@
       <c r="AB26" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-1600</v>
       </c>
       <c r="R27" s="3">
         <v>-1600</v>
       </c>
       <c r="S27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="T27" s="3">
         <v>-800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>19300</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-1000</v>
       </c>
       <c r="AA27" s="3">
         <v>-1000</v>
@@ -2220,8 +2275,11 @@
       <c r="AB27" s="3">
         <v>-1000</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2347,14 +2408,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>4</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2369,19 +2430,22 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-8200</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>300</v>
       </c>
       <c r="AA29" s="3">
         <v>300</v>
       </c>
       <c r="AB29" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC29" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,8 +2607,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2569,8 +2639,8 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2588,120 +2658,126 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>5000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-1600</v>
       </c>
       <c r="R33" s="3">
         <v>-1600</v>
       </c>
       <c r="S33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="T33" s="3">
         <v>-800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>11200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-1600</v>
       </c>
       <c r="R35" s="3">
         <v>-1600</v>
       </c>
       <c r="S35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="T35" s="3">
         <v>-800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>11200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,31 +3091,32 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E41" s="3">
         <v>3700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2100</v>
-      </c>
-      <c r="J41" s="3">
-        <v>300</v>
       </c>
       <c r="K41" s="3">
         <v>300</v>
@@ -3038,37 +3125,37 @@
         <v>300</v>
       </c>
       <c r="M41" s="3">
+        <v>300</v>
+      </c>
+      <c r="N41" s="3">
         <v>1400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>700</v>
-      </c>
-      <c r="W41" s="3">
-        <v>100</v>
       </c>
       <c r="X41" s="3">
         <v>100</v>
@@ -3077,16 +3164,19 @@
         <v>100</v>
       </c>
       <c r="Z41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA41" s="3">
         <v>300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3136,26 +3226,26 @@
         <v>0</v>
       </c>
       <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
         <v>500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>5100</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X42" s="3">
+      <c r="X42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y42" s="3">
         <v>7000</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3165,37 +3255,40 @@
       <c r="AB42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E43" s="3">
         <v>500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>700</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M43" s="3">
         <v>200</v>
@@ -3204,7 +3297,7 @@
         <v>200</v>
       </c>
       <c r="O43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -3215,11 +3308,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -3234,76 +3327,79 @@
         <v>0</v>
       </c>
       <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
         <v>200</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
-      </c>
       <c r="AA43" s="3">
         <v>0</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E44" s="3">
         <v>20400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>20000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>11500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1900</v>
-      </c>
-      <c r="N44" s="3">
-        <v>1800</v>
       </c>
       <c r="O44" s="3">
         <v>1800</v>
       </c>
       <c r="P44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q44" s="3">
         <v>1500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>100</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3319,14 +3415,17 @@
       <c r="Z44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA44" s="3">
-        <v>0</v>
+      <c r="AA44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3354,8 +3453,8 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
-        <v>100</v>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M45" s="3">
         <v>100</v>
@@ -3373,16 +3472,16 @@
         <v>100</v>
       </c>
       <c r="R45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3">
         <v>100</v>
       </c>
       <c r="U45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
@@ -3397,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="Z45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="3">
         <v>100</v>
@@ -3405,88 +3504,94 @@
       <c r="AB45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E46" s="3">
         <v>25100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>28400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>32200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16200</v>
       </c>
-      <c r="H46" s="3">
-        <v>10200</v>
-      </c>
       <c r="I46" s="3">
+        <v>10400</v>
+      </c>
+      <c r="J46" s="3">
         <v>5900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2100</v>
-      </c>
-      <c r="K46" s="3">
-        <v>2600</v>
       </c>
       <c r="L46" s="3">
         <v>2600</v>
       </c>
       <c r="M46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N46" s="3">
         <v>3600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3514,8 +3619,8 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3544,86 +3649,89 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W47" s="3">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X47" s="3">
         <v>4200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>14000</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>142000</v>
       </c>
       <c r="AA47" s="3">
         <v>142000</v>
       </c>
       <c r="AB47" s="3">
+        <v>142000</v>
+      </c>
+      <c r="AC47" s="3">
         <v>141300</v>
       </c>
     </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E48" s="3">
         <v>28300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>27900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11300</v>
       </c>
-      <c r="H48" s="3">
-        <v>10900</v>
-      </c>
       <c r="I48" s="3">
+        <v>10800</v>
+      </c>
+      <c r="J48" s="3">
         <v>7600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5800</v>
-      </c>
-      <c r="O48" s="3">
-        <v>4000</v>
       </c>
       <c r="P48" s="3">
         <v>4000</v>
       </c>
       <c r="Q48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="R48" s="3">
         <v>4400</v>
-      </c>
-      <c r="R48" s="3">
-        <v>4200</v>
       </c>
       <c r="S48" s="3">
         <v>4200</v>
       </c>
       <c r="T48" s="3">
+        <v>4200</v>
+      </c>
+      <c r="U48" s="3">
         <v>3500</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
       <c r="V48" s="3">
         <v>0</v>
       </c>
@@ -3645,8 +3753,11 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3678,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="N49" s="3">
         <v>5200</v>
@@ -3690,7 +3801,7 @@
         <v>5200</v>
       </c>
       <c r="Q49" s="3">
-        <v>6400</v>
+        <v>5200</v>
       </c>
       <c r="R49" s="3">
         <v>6400</v>
@@ -3701,8 +3812,8 @@
       <c r="T49" s="3">
         <v>6400</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>4</v>
+      <c r="U49" s="3">
+        <v>6400</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>4</v>
@@ -3719,14 +3830,17 @@
       <c r="Z49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
+      <c r="AA49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,8 +4002,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3900,28 +4020,28 @@
         <v>1400</v>
       </c>
       <c r="G52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H52" s="3">
         <v>400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>300</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
+      <c r="L52" s="3">
+        <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="N52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -3941,8 +4061,8 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>4</v>
+      <c r="U52" s="3">
+        <v>0</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>4</v>
@@ -3959,14 +4079,17 @@
       <c r="Z52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4168,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E54" s="3">
         <v>54700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>57700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>60200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>14300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>142400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>143000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>142900</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,52 +4315,53 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1800</v>
-      </c>
-      <c r="G57" s="3">
-        <v>900</v>
       </c>
       <c r="H57" s="3">
         <v>900</v>
       </c>
       <c r="I57" s="3">
+        <v>900</v>
+      </c>
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>300</v>
-      </c>
-      <c r="L57" s="3">
-        <v>500</v>
       </c>
       <c r="M57" s="3">
         <v>500</v>
       </c>
       <c r="N57" s="3">
+        <v>500</v>
+      </c>
+      <c r="O57" s="3">
         <v>1000</v>
-      </c>
-      <c r="O57" s="3">
-        <v>300</v>
       </c>
       <c r="P57" s="3">
         <v>300</v>
       </c>
       <c r="Q57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R57" s="3">
         <v>200</v>
@@ -4239,10 +4370,10 @@
         <v>200</v>
       </c>
       <c r="T57" s="3">
+        <v>200</v>
+      </c>
+      <c r="U57" s="3">
         <v>300</v>
-      </c>
-      <c r="U57" s="3">
-        <v>100</v>
       </c>
       <c r="V57" s="3">
         <v>100</v>
@@ -4251,52 +4382,55 @@
         <v>100</v>
       </c>
       <c r="X57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y57" s="3">
         <v>0</v>
       </c>
       <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3">
         <v>200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E58" s="3">
         <v>5000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4309,8 +4443,8 @@
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -4324,14 +4458,14 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>4</v>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>4</v>
@@ -4345,23 +4479,26 @@
       <c r="AB58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>300</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4374,29 +4511,29 @@
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>300</v>
       </c>
       <c r="N59" s="3">
         <v>300</v>
       </c>
       <c r="O59" s="3">
+        <v>300</v>
+      </c>
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>100</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>200</v>
       </c>
       <c r="R59" s="3">
         <v>200</v>
       </c>
       <c r="S59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="T59" s="3">
         <v>300</v>
@@ -4405,69 +4542,72 @@
         <v>300</v>
       </c>
       <c r="V59" s="3">
+        <v>300</v>
+      </c>
+      <c r="W59" s="3">
         <v>1200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E60" s="3">
         <v>7400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>500</v>
-      </c>
-      <c r="P60" s="3">
-        <v>400</v>
       </c>
       <c r="Q60" s="3">
         <v>400</v>
@@ -4476,81 +4616,84 @@
         <v>400</v>
       </c>
       <c r="S60" s="3">
+        <v>400</v>
+      </c>
+      <c r="T60" s="3">
         <v>500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E61" s="3">
         <v>15300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1500</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>200</v>
       </c>
       <c r="R61" s="3">
         <v>200</v>
@@ -4559,7 +4702,7 @@
         <v>200</v>
       </c>
       <c r="T61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U61" s="3">
         <v>300</v>
@@ -4568,7 +4711,7 @@
         <v>300</v>
       </c>
       <c r="W61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="X61" s="3">
         <v>0</v>
@@ -4585,8 +4728,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4614,8 +4760,8 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
-        <v>1300</v>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>1300</v>
@@ -4627,7 +4773,7 @@
         <v>1300</v>
       </c>
       <c r="P62" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="Q62" s="3">
         <v>1400</v>
@@ -4642,10 +4788,10 @@
         <v>1400</v>
       </c>
       <c r="U62" s="3">
-        <v>0</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>4</v>
+        <v>1400</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>4</v>
@@ -4656,8 +4802,8 @@
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5060,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E66" s="3">
         <v>22700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3300</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>1900</v>
       </c>
       <c r="R66" s="3">
         <v>1900</v>
       </c>
       <c r="S66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="T66" s="3">
         <v>2000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>142200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>142100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>141400</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5506,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-65000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-62400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-58300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-54900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-58200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-58700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-60100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-60400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-57100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-55700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-48900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-47200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-45100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-43600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-40600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-39000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-37500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-36700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-35800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-33300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-34000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-27700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-36800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-36200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5838,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E76" s="3">
         <v>32000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>32800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>35000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-1600</v>
       </c>
       <c r="R81" s="3">
         <v>-1600</v>
       </c>
       <c r="S81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="T81" s="3">
         <v>-800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>11200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,8 +6208,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6022,7 +6221,7 @@
         <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -6061,7 +6260,7 @@
         <v>100</v>
       </c>
       <c r="S83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-1000</v>
       </c>
       <c r="L89" s="3">
         <v>-1000</v>
       </c>
       <c r="M89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="N89" s="3">
         <v>-1900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-600</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-400</v>
       </c>
       <c r="V89" s="3">
         <v>-400</v>
       </c>
       <c r="W89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="X89" s="3">
         <v>-300</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>-700</v>
       </c>
       <c r="AB89" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,62 +6820,63 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-200</v>
       </c>
       <c r="K91" s="3">
         <v>-200</v>
       </c>
       <c r="L91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
@@ -6665,8 +6886,8 @@
       <c r="W91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -6677,11 +6898,14 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7067,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1000</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-200</v>
       </c>
       <c r="K94" s="3">
         <v>-200</v>
       </c>
       <c r="L94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M94" s="3">
         <v>-400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2000</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>2100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1000</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>6000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>100</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6979,8 +7213,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,61 +7513,64 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3">
         <v>1500</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>11400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>800</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q100" s="3">
         <v>2100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>600</v>
-      </c>
-      <c r="R100" s="3">
-        <v>2500</v>
       </c>
       <c r="S100" s="3">
         <v>2500</v>
       </c>
       <c r="T100" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
@@ -7333,25 +7579,28 @@
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>300</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>1400</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7379,8 +7628,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7430,84 +7679,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>-600</v>
       </c>
       <c r="AA102" s="3">
         <v>-600</v>
       </c>
       <c r="AB102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOWG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
   <si>
     <t>SOWG</t>
   </si>
@@ -656,177 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E8" s="3">
         <v>2500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>200</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
         <v>100</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
       <c r="S8" s="3">
         <v>0</v>
       </c>
@@ -846,75 +850,78 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
         <v>300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>200</v>
       </c>
-      <c r="AA8" s="3">
-        <v>0</v>
-      </c>
       <c r="AB8" s="3">
         <v>0</v>
       </c>
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>100</v>
       </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
       <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
         <v>100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>200</v>
       </c>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
       <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3">
         <v>100</v>
       </c>
-      <c r="R9" s="3">
-        <v>0</v>
-      </c>
       <c r="S9" s="3">
         <v>0</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>4</v>
+      <c r="T9" s="3">
+        <v>0</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>4</v>
@@ -943,41 +950,44 @@
       <c r="AC9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E10" s="3">
         <v>1100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-1200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
       <c r="N10" s="3">
         <v>0</v>
       </c>
@@ -996,8 +1006,8 @@
       <c r="S10" s="3">
         <v>0</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>4</v>
+      <c r="T10" s="3">
+        <v>0</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>4</v>
@@ -1026,8 +1036,11 @@
       <c r="AC10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,8 +1070,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,91 +1240,97 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>700</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>1400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>1900</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
         <v>5200</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>1500</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-100</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>-20400</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1336,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3">
         <v>100</v>
@@ -1360,7 +1383,7 @@
         <v>100</v>
       </c>
       <c r="T15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,82 +1443,83 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E17" s="3">
         <v>4900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1000</v>
-      </c>
-      <c r="W17" s="3">
-        <v>400</v>
       </c>
       <c r="X17" s="3">
         <v>400</v>
       </c>
       <c r="Y17" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z17" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>-17200</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>400</v>
       </c>
       <c r="AB17" s="3">
         <v>400</v>
@@ -1500,82 +1527,85 @@
       <c r="AC17" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-400</v>
       </c>
       <c r="X18" s="3">
         <v>-400</v>
       </c>
       <c r="Y18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z18" s="3">
         <v>1300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>17400</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-400</v>
       </c>
       <c r="AB18" s="3">
         <v>-400</v>
@@ -1583,8 +1613,11 @@
       <c r="AC18" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,8 +1647,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1646,8 +1680,8 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1665,114 +1699,117 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2000</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2800</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-1500</v>
       </c>
       <c r="S21" s="3">
         <v>-1500</v>
       </c>
       <c r="T21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="U21" s="3">
         <v>-800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>19500</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>-400</v>
       </c>
       <c r="AB21" s="3">
         <v>-400</v>
@@ -1780,13 +1817,16 @@
       <c r="AC21" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
         <v>200</v>
@@ -1795,25 +1835,25 @@
         <v>200</v>
       </c>
       <c r="G22" s="3">
+        <v>200</v>
+      </c>
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>500</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>500</v>
-      </c>
-      <c r="M22" s="3">
-        <v>400</v>
       </c>
       <c r="N22" s="3">
         <v>400</v>
@@ -1822,11 +1862,11 @@
         <v>400</v>
       </c>
       <c r="P22" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1843,16 +1883,16 @@
         <v>0</v>
       </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>400</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -1863,82 +1903,85 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2900</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-1600</v>
       </c>
       <c r="S23" s="3">
         <v>-1600</v>
       </c>
       <c r="T23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="U23" s="3">
         <v>-800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>19500</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-400</v>
       </c>
       <c r="AB23" s="3">
         <v>-400</v>
@@ -1946,26 +1989,29 @@
       <c r="AC23" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="3">
-        <v>-100</v>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F24" s="3">
         <v>-100</v>
       </c>
       <c r="G24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>4</v>
       </c>
@@ -1981,8 +2027,8 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -2029,8 +2075,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,82 +2161,85 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2900</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-1600</v>
       </c>
       <c r="S26" s="3">
         <v>-1600</v>
       </c>
       <c r="T26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="U26" s="3">
         <v>-800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>19500</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-400</v>
       </c>
       <c r="AB26" s="3">
         <v>-400</v>
@@ -2195,82 +2247,85 @@
       <c r="AC26" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2900</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-1600</v>
       </c>
       <c r="S27" s="3">
         <v>-1600</v>
       </c>
       <c r="T27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="U27" s="3">
         <v>-800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>19300</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-1000</v>
       </c>
       <c r="AB27" s="3">
         <v>-1000</v>
@@ -2278,8 +2333,11 @@
       <c r="AC27" s="3">
         <v>-1000</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2411,14 +2472,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>4</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2433,19 +2494,22 @@
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-8200</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>300</v>
       </c>
       <c r="AB29" s="3">
         <v>300</v>
       </c>
       <c r="AC29" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD29" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,8 +2677,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2642,8 +2712,8 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2661,123 +2731,129 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2900</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-1600</v>
       </c>
       <c r="S33" s="3">
         <v>-1600</v>
       </c>
       <c r="T33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="U33" s="3">
         <v>-800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>11200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2900</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-1600</v>
       </c>
       <c r="S35" s="3">
         <v>-1600</v>
       </c>
       <c r="T35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="U35" s="3">
         <v>-800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>11200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,34 +3178,35 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2100</v>
-      </c>
-      <c r="K41" s="3">
-        <v>300</v>
       </c>
       <c r="L41" s="3">
         <v>300</v>
@@ -3128,37 +3215,37 @@
         <v>300</v>
       </c>
       <c r="N41" s="3">
+        <v>300</v>
+      </c>
+      <c r="O41" s="3">
         <v>1400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>700</v>
-      </c>
-      <c r="X41" s="3">
-        <v>100</v>
       </c>
       <c r="Y41" s="3">
         <v>100</v>
@@ -3167,16 +3254,19 @@
         <v>100</v>
       </c>
       <c r="AA41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB41" s="3">
         <v>300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3229,26 +3319,26 @@
         <v>0</v>
       </c>
       <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
         <v>500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>5100</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y42" s="3">
+      <c r="Y42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z42" s="3">
         <v>7000</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3258,40 +3348,43 @@
       <c r="AC42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>700</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N43" s="3">
         <v>200</v>
@@ -3300,7 +3393,7 @@
         <v>200</v>
       </c>
       <c r="P43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -3311,11 +3404,11 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -3330,79 +3423,82 @@
         <v>0</v>
       </c>
       <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3">
         <v>200</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
-      </c>
       <c r="AB43" s="3">
         <v>0</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E44" s="3">
         <v>21200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>20400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>20000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>11500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1900</v>
-      </c>
-      <c r="O44" s="3">
-        <v>1800</v>
       </c>
       <c r="P44" s="3">
         <v>1800</v>
       </c>
       <c r="Q44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R44" s="3">
         <v>1500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>100</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3418,14 +3514,17 @@
       <c r="AA44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB44" s="3">
-        <v>0</v>
+      <c r="AB44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3456,8 +3555,8 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
-        <v>100</v>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N45" s="3">
         <v>100</v>
@@ -3475,16 +3574,16 @@
         <v>100</v>
       </c>
       <c r="S45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U45" s="3">
         <v>100</v>
       </c>
       <c r="V45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -3499,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="AA45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB45" s="3">
         <v>100</v>
@@ -3507,91 +3606,97 @@
       <c r="AC45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E46" s="3">
         <v>24600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>28400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>32200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2100</v>
-      </c>
-      <c r="L46" s="3">
-        <v>2600</v>
       </c>
       <c r="M46" s="3">
         <v>2600</v>
       </c>
       <c r="N46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="O46" s="3">
         <v>3600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3622,8 +3727,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3652,89 +3757,92 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X47" s="3">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y47" s="3">
         <v>4200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>14000</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>142000</v>
       </c>
       <c r="AB47" s="3">
         <v>142000</v>
       </c>
       <c r="AC47" s="3">
+        <v>142000</v>
+      </c>
+      <c r="AD47" s="3">
         <v>141300</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E48" s="3">
         <v>26700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>28300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>27900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5800</v>
-      </c>
-      <c r="P48" s="3">
-        <v>4000</v>
       </c>
       <c r="Q48" s="3">
         <v>4000</v>
       </c>
       <c r="R48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="S48" s="3">
         <v>4400</v>
-      </c>
-      <c r="S48" s="3">
-        <v>4200</v>
       </c>
       <c r="T48" s="3">
         <v>4200</v>
       </c>
       <c r="U48" s="3">
+        <v>4200</v>
+      </c>
+      <c r="V48" s="3">
         <v>3500</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
       <c r="W48" s="3">
         <v>0</v>
       </c>
@@ -3756,8 +3864,11 @@
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3792,7 +3903,7 @@
         <v>0</v>
       </c>
       <c r="N49" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="O49" s="3">
         <v>5200</v>
@@ -3804,7 +3915,7 @@
         <v>5200</v>
       </c>
       <c r="R49" s="3">
-        <v>6400</v>
+        <v>5200</v>
       </c>
       <c r="S49" s="3">
         <v>6400</v>
@@ -3815,8 +3926,8 @@
       <c r="U49" s="3">
         <v>6400</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>4</v>
+      <c r="V49" s="3">
+        <v>6400</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>4</v>
@@ -3833,14 +3944,17 @@
       <c r="AA49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
+      <c r="AB49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,13 +4122,16 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="E52" s="3">
         <v>1400</v>
@@ -4023,28 +4143,28 @@
         <v>1400</v>
       </c>
       <c r="H52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I52" s="3">
         <v>400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>300</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -4064,8 +4184,8 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>4</v>
+      <c r="V52" s="3">
+        <v>0</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>4</v>
@@ -4082,14 +4202,17 @@
       <c r="AA52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
+      <c r="AB52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4294,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E54" s="3">
         <v>52700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>54700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>57700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>60200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>12300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>14300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>142400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>143000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>142900</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,8 +4446,9 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4325,46 +4456,46 @@
         <v>1200</v>
       </c>
       <c r="E57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1800</v>
-      </c>
-      <c r="H57" s="3">
-        <v>900</v>
       </c>
       <c r="I57" s="3">
         <v>900</v>
       </c>
       <c r="J57" s="3">
+        <v>900</v>
+      </c>
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>300</v>
-      </c>
-      <c r="M57" s="3">
-        <v>500</v>
       </c>
       <c r="N57" s="3">
         <v>500</v>
       </c>
       <c r="O57" s="3">
+        <v>500</v>
+      </c>
+      <c r="P57" s="3">
         <v>1000</v>
-      </c>
-      <c r="P57" s="3">
-        <v>300</v>
       </c>
       <c r="Q57" s="3">
         <v>300</v>
       </c>
       <c r="R57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="S57" s="3">
         <v>200</v>
@@ -4373,10 +4504,10 @@
         <v>200</v>
       </c>
       <c r="U57" s="3">
+        <v>200</v>
+      </c>
+      <c r="V57" s="3">
         <v>300</v>
-      </c>
-      <c r="V57" s="3">
-        <v>100</v>
       </c>
       <c r="W57" s="3">
         <v>100</v>
@@ -4385,55 +4516,58 @@
         <v>100</v>
       </c>
       <c r="Y57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z57" s="3">
         <v>0</v>
       </c>
       <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="3">
         <v>200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4446,8 +4580,8 @@
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -4461,14 +4595,14 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3" t="s">
-        <v>4</v>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>4</v>
@@ -4482,8 +4616,11 @@
       <c r="AC58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4493,15 +4630,15 @@
       <c r="E59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>300</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4514,29 +4651,29 @@
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>400</v>
-      </c>
-      <c r="N59" s="3">
-        <v>300</v>
       </c>
       <c r="O59" s="3">
         <v>300</v>
       </c>
       <c r="P59" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>100</v>
-      </c>
-      <c r="R59" s="3">
-        <v>200</v>
       </c>
       <c r="S59" s="3">
         <v>200</v>
       </c>
       <c r="T59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U59" s="3">
         <v>300</v>
@@ -4545,72 +4682,75 @@
         <v>300</v>
       </c>
       <c r="W59" s="3">
+        <v>300</v>
+      </c>
+      <c r="X59" s="3">
         <v>1200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E60" s="3">
         <v>6800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>500</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>400</v>
       </c>
       <c r="R60" s="3">
         <v>400</v>
@@ -4619,84 +4759,87 @@
         <v>400</v>
       </c>
       <c r="T60" s="3">
+        <v>400</v>
+      </c>
+      <c r="U60" s="3">
         <v>500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E61" s="3">
         <v>15200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1500</v>
-      </c>
-      <c r="R61" s="3">
-        <v>200</v>
       </c>
       <c r="S61" s="3">
         <v>200</v>
@@ -4705,7 +4848,7 @@
         <v>200</v>
       </c>
       <c r="U61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V61" s="3">
         <v>300</v>
@@ -4714,7 +4857,7 @@
         <v>300</v>
       </c>
       <c r="X61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
@@ -4731,8 +4874,11 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4763,8 +4909,8 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
-        <v>1300</v>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N62" s="3">
         <v>1300</v>
@@ -4776,7 +4922,7 @@
         <v>1300</v>
       </c>
       <c r="Q62" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="R62" s="3">
         <v>1400</v>
@@ -4791,10 +4937,10 @@
         <v>1400</v>
       </c>
       <c r="V62" s="3">
-        <v>0</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>4</v>
+        <v>1400</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>4</v>
@@ -4805,8 +4951,8 @@
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5218,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E66" s="3">
         <v>21900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>22700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3300</v>
-      </c>
-      <c r="R66" s="3">
-        <v>1900</v>
       </c>
       <c r="S66" s="3">
         <v>1900</v>
       </c>
       <c r="T66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="U66" s="3">
         <v>2000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>142200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>142100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>141400</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5680,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-69200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-65000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-62400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-58300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-54900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-58200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-58700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-60100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-60400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-57100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-55700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-48900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-47200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-45100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-43600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-40600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-39000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-37500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-36700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-35800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-33300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-34000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-31400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-27700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-36800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-36200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6024,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E76" s="3">
         <v>30800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>32000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>32800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>35000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2900</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-1600</v>
       </c>
       <c r="S81" s="3">
         <v>-1600</v>
       </c>
       <c r="T81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="U81" s="3">
         <v>-800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>11200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,13 +6407,14 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="E83" s="3">
         <v>200</v>
@@ -6224,7 +6423,7 @@
         <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -6263,7 +6462,7 @@
         <v>100</v>
       </c>
       <c r="T83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1500</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-1000</v>
       </c>
       <c r="M89" s="3">
         <v>-1000</v>
       </c>
       <c r="N89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O89" s="3">
         <v>-1900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-600</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-400</v>
       </c>
       <c r="W89" s="3">
         <v>-400</v>
       </c>
       <c r="X89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-300</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>-700</v>
       </c>
       <c r="AC89" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,8 +7041,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6830,56 +7051,56 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-200</v>
       </c>
       <c r="L91" s="3">
         <v>-200</v>
       </c>
       <c r="M91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-700</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
@@ -6889,8 +7110,8 @@
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -6901,11 +7122,14 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,8 +7297,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7079,82 +7309,85 @@
         <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1000</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-200</v>
       </c>
       <c r="L94" s="3">
         <v>-200</v>
       </c>
       <c r="M94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N94" s="3">
         <v>-400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2000</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>2100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1000</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>6000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>100</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7216,8 +7450,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,64 +7759,67 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3">
         <v>1500</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>11400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>800</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="3">
         <v>2100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
-      </c>
-      <c r="S100" s="3">
-        <v>2500</v>
       </c>
       <c r="T100" s="3">
         <v>2500</v>
       </c>
       <c r="U100" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -7582,25 +7828,28 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>300</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>1400</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7631,8 +7880,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7682,87 +7931,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA102" s="3">
-        <v>-600</v>
       </c>
       <c r="AB102" s="3">
         <v>-600</v>
       </c>
       <c r="AC102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOWG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
   <si>
     <t>SOWG</t>
   </si>
@@ -656,194 +656,201 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3">
         <v>1600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1900</v>
       </c>
-      <c r="F8" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3">
         <v>3600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>15600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>11400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>9500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>5000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
         <v>100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>200</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
         <v>100</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
@@ -860,84 +867,90 @@
         <v>0</v>
       </c>
       <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
         <v>300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>200</v>
       </c>
-      <c r="AC8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>0</v>
-      </c>
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3">
         <v>10500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2000</v>
       </c>
-      <c r="F9" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2600</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9" s="3">
         <v>3000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>6600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>6800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>4700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1000</v>
-      </c>
-      <c r="N9" s="3">
-        <v>100</v>
-      </c>
-      <c r="O9" s="3">
-        <v>0</v>
       </c>
       <c r="P9" s="3">
         <v>100</v>
       </c>
       <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3">
+        <v>100</v>
+      </c>
+      <c r="S9" s="3">
         <v>200</v>
       </c>
-      <c r="R9" s="3">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3">
         <v>100</v>
       </c>
-      <c r="T9" s="3">
-        <v>0</v>
-      </c>
-      <c r="U9" s="3">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>4</v>
+      <c r="V9" s="3">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3">
+        <v>0</v>
       </c>
       <c r="X9" s="3" t="s">
         <v>4</v>
@@ -963,50 +976,56 @@
       <c r="AE9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="3">
         <v>-8900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-100</v>
       </c>
-      <c r="F10" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G10" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J10" s="3">
         <v>600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>9000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>4800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
       <c r="Q10" s="3">
         <v>0</v>
       </c>
@@ -1022,11 +1041,11 @@
       <c r="U10" s="3">
         <v>0</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>4</v>
+      <c r="V10" s="3">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>4</v>
@@ -1052,8 +1071,14 @@
       <c r="AE10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,8 +1110,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1174,8 +1201,14 @@
       <c r="AE12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,97 +1296,109 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1800</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>1400</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
         <v>1900</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3">
         <v>5200</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>1500</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-100</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1373,7 +1418,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1388,10 +1433,10 @@
         <v>0</v>
       </c>
       <c r="N15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P15" s="3">
         <v>100</v>
@@ -1412,10 +1457,10 @@
         <v>100</v>
       </c>
       <c r="V15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1441,8 +1486,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1522,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="3">
         <v>14100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5900</v>
       </c>
-      <c r="F17" s="3">
-        <v>4900</v>
-      </c>
-      <c r="G17" s="3">
-        <v>5500</v>
-      </c>
       <c r="H17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="3">
         <v>6800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>10800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>10500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>6300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>6400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1500</v>
-      </c>
-      <c r="V17" s="3">
-        <v>1000</v>
-      </c>
-      <c r="W17" s="3">
-        <v>1200</v>
       </c>
       <c r="X17" s="3">
         <v>1000</v>
       </c>
       <c r="Y17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA17" s="3">
         <v>400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>-17200</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>400</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>400</v>
       </c>
       <c r="AE17" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3">
         <v>-12600</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-2400</v>
       </c>
       <c r="G18" s="3">
         <v>-4100</v>
       </c>
       <c r="H18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3">
         <v>-3300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>4900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>3200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-6400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-2900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1500</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-1200</v>
       </c>
       <c r="X18" s="3">
         <v>-1000</v>
       </c>
       <c r="Y18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>1300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>17400</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-400</v>
       </c>
       <c r="AE18" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,8 +1747,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1720,11 +1787,11 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1739,183 +1806,195 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>1500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>2000</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-12600</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-2400</v>
       </c>
       <c r="G21" s="3">
         <v>-4100</v>
       </c>
       <c r="H21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>200</v>
+      </c>
+      <c r="J21" s="3">
         <v>-3200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>4900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>3200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-6300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-1700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-1400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-2800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-1500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-1500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>19500</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>-400</v>
       </c>
       <c r="AE21" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
+        <v>400</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
-        <v>200</v>
-      </c>
-      <c r="H22" s="3">
-        <v>200</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>500</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>500</v>
-      </c>
-      <c r="O22" s="3">
-        <v>400</v>
-      </c>
-      <c r="P22" s="3">
-        <v>400</v>
       </c>
       <c r="Q22" s="3">
         <v>400</v>
       </c>
       <c r="R22" s="3">
+        <v>400</v>
+      </c>
+      <c r="S22" s="3">
+        <v>400</v>
+      </c>
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
@@ -1929,19 +2008,19 @@
         <v>0</v>
       </c>
       <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
         <v>400</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -1949,97 +2028,109 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="3">
         <v>-10900</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-2600</v>
       </c>
       <c r="G23" s="3">
         <v>-4200</v>
       </c>
       <c r="H23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="3">
         <v>-3400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>3600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-3300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-6800</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-2100</v>
       </c>
       <c r="R23" s="3">
         <v>-1600</v>
       </c>
       <c r="S23" s="3">
-        <v>-2900</v>
+        <v>-2100</v>
       </c>
       <c r="T23" s="3">
         <v>-1600</v>
       </c>
       <c r="U23" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V23" s="3">
         <v>-1600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="X23" s="3">
         <v>-800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>19500</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>-400</v>
       </c>
       <c r="AE23" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2052,21 +2143,21 @@
       <c r="F24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2079,11 +2170,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2127,8 +2218,14 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2313,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="3">
         <v>-10900</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-2600</v>
       </c>
       <c r="G26" s="3">
         <v>-4200</v>
       </c>
       <c r="H26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3">
         <v>-3400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-3300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-6800</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-2100</v>
       </c>
       <c r="R26" s="3">
         <v>-1600</v>
       </c>
       <c r="S26" s="3">
-        <v>-2900</v>
+        <v>-2100</v>
       </c>
       <c r="T26" s="3">
         <v>-1600</v>
       </c>
       <c r="U26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V26" s="3">
         <v>-1600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="X26" s="3">
         <v>-800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>19500</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>-400</v>
       </c>
       <c r="AE26" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="3">
         <v>-10900</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-2600</v>
       </c>
       <c r="G27" s="3">
         <v>-4200</v>
       </c>
       <c r="H27" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3">
         <v>-3400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-3300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-6800</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-2100</v>
       </c>
       <c r="R27" s="3">
         <v>-1600</v>
       </c>
       <c r="S27" s="3">
-        <v>-2900</v>
+        <v>-2100</v>
       </c>
       <c r="T27" s="3">
         <v>-1600</v>
       </c>
       <c r="U27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V27" s="3">
         <v>-1600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="X27" s="3">
         <v>-800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>19300</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>-1000</v>
       </c>
       <c r="AE27" s="3">
         <v>-1000</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,13 +2598,19 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2501,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -2539,17 +2660,17 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -2561,19 +2682,25 @@
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-8200</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>300</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AF29" s="3">
         <v>300</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AG29" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,8 +2883,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2788,11 +2927,11 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2807,129 +2946,141 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>1500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>2200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>5000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3">
         <v>-10900</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-2600</v>
       </c>
       <c r="G33" s="3">
         <v>-4200</v>
       </c>
       <c r="H33" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" s="3">
         <v>-3400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-3300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-6800</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-2100</v>
       </c>
       <c r="R33" s="3">
         <v>-1600</v>
       </c>
       <c r="S33" s="3">
-        <v>-2900</v>
+        <v>-2100</v>
       </c>
       <c r="T33" s="3">
         <v>-1600</v>
       </c>
       <c r="U33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V33" s="3">
         <v>-1600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="X33" s="3">
         <v>-800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>11200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3168,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="3">
         <v>-10900</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-2600</v>
       </c>
       <c r="G35" s="3">
         <v>-4200</v>
       </c>
       <c r="H35" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3">
         <v>-3400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-3300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-6800</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-2100</v>
       </c>
       <c r="R35" s="3">
         <v>-1600</v>
       </c>
       <c r="S35" s="3">
-        <v>-2900</v>
+        <v>-2100</v>
       </c>
       <c r="T35" s="3">
         <v>-1600</v>
       </c>
       <c r="U35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V35" s="3">
         <v>-1600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="X35" s="3">
         <v>-800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>11200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,97 +3437,105 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F41" s="3">
         <v>400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>14400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>6800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2100</v>
-      </c>
-      <c r="M41" s="3">
-        <v>300</v>
-      </c>
-      <c r="N41" s="3">
-        <v>300</v>
       </c>
       <c r="O41" s="3">
         <v>300</v>
       </c>
       <c r="P41" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>300</v>
+      </c>
+      <c r="R41" s="3">
         <v>1400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>700</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>100</v>
       </c>
       <c r="AB41" s="3">
         <v>100</v>
       </c>
       <c r="AC41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE41" s="3">
         <v>300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3415,87 +3594,93 @@
         <v>0</v>
       </c>
       <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
         <v>500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>2200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>5100</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC42" s="3">
         <v>7000</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1300</v>
       </c>
-      <c r="G43" s="3">
-        <v>500</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>1200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>6200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>700</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
-      <c r="O43" s="3">
-        <v>200</v>
-      </c>
       <c r="P43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="3">
         <v>200</v>
       </c>
       <c r="R43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -3503,14 +3688,14 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>4</v>
+      <c r="V43" s="3">
+        <v>0</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -3522,88 +3707,94 @@
         <v>0</v>
       </c>
       <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3">
         <v>200</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>0</v>
-      </c>
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
         <v>11500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>20800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>21200</v>
       </c>
-      <c r="G44" s="3">
-        <v>20400</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>20000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>11500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>5900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>4700</v>
-      </c>
-      <c r="L44" s="3">
-        <v>2200</v>
-      </c>
-      <c r="M44" s="3">
-        <v>900</v>
       </c>
       <c r="N44" s="3">
         <v>2200</v>
       </c>
       <c r="O44" s="3">
+        <v>900</v>
+      </c>
+      <c r="P44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q44" s="3">
         <v>2000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>1200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>100</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3616,34 +3807,40 @@
       <c r="AC44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
+      <c r="I45" s="3">
+        <v>20800</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
@@ -3660,11 +3857,11 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
-        <v>100</v>
-      </c>
-      <c r="P45" s="3">
-        <v>100</v>
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
@@ -3679,19 +3876,19 @@
         <v>100</v>
       </c>
       <c r="U45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>100</v>
       </c>
       <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3">
         <v>100</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
       <c r="Y45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z45" s="3">
         <v>0</v>
@@ -3703,105 +3900,117 @@
         <v>0</v>
       </c>
       <c r="AC45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F46" s="3">
         <v>13000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>22800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>24600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>25100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>28400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>32200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>16200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>10400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>5900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3600</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>4900</v>
-      </c>
-      <c r="R46" s="3">
-        <v>3700</v>
       </c>
       <c r="S46" s="3">
         <v>4900</v>
       </c>
       <c r="T46" s="3">
+        <v>3700</v>
+      </c>
+      <c r="U46" s="3">
+        <v>4900</v>
+      </c>
+      <c r="V46" s="3">
         <v>3800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>2400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>2700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>5700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>7100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3838,11 +4047,11 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3868,98 +4077,104 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>4</v>
+      <c r="Y47" s="3">
+        <v>0</v>
       </c>
       <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB47" s="3">
         <v>4200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>7000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>14000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>142000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>142000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>141300</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3">
+        <v>100</v>
+      </c>
+      <c r="F48" s="3">
         <v>11500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>25800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>26700</v>
       </c>
-      <c r="G48" s="3">
-        <v>28300</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
+        <v>300</v>
+      </c>
+      <c r="J48" s="3">
         <v>27900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>26600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>11300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>10800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>7600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>6500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>6400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>6300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>6000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>5800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>4000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>4000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>4400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>4200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>4200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>3500</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>0</v>
-      </c>
       <c r="Z48" s="3">
         <v>0</v>
       </c>
@@ -3978,8 +4193,14 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4020,10 +4241,10 @@
         <v>0</v>
       </c>
       <c r="P49" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="R49" s="3">
         <v>5200</v>
@@ -4032,10 +4253,10 @@
         <v>5200</v>
       </c>
       <c r="T49" s="3">
-        <v>6400</v>
+        <v>5200</v>
       </c>
       <c r="U49" s="3">
-        <v>6400</v>
+        <v>5200</v>
       </c>
       <c r="V49" s="3">
         <v>6400</v>
@@ -4043,11 +4264,11 @@
       <c r="W49" s="3">
         <v>6400</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y49" s="3" t="s">
-        <v>4</v>
+      <c r="X49" s="3">
+        <v>6400</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>6400</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>4</v>
@@ -4061,14 +4282,20 @@
       <c r="AC49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,55 +4478,61 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>300</v>
+      </c>
+      <c r="F52" s="3">
         <v>1000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1400</v>
       </c>
       <c r="H52" s="3">
         <v>1400</v>
       </c>
       <c r="I52" s="3">
+        <v>29300</v>
+      </c>
+      <c r="J52" s="3">
         <v>1400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L52" s="3">
         <v>400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>300</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -4310,11 +4549,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y52" s="3" t="s">
-        <v>4</v>
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>4</v>
@@ -4328,14 +4567,20 @@
       <c r="AC52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,97 +4668,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F54" s="3">
         <v>25600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>50000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>52700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>54700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>57700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>60200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>27900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>21500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>13500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>8600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>9100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>8900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>14900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>16000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>12800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>14100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>14600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>15300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>14200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>12300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>5800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>4300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>7100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>14300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>142400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>143000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>142900</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,139 +4837,147 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>300</v>
-      </c>
-      <c r="T57" s="3">
-        <v>200</v>
-      </c>
-      <c r="U57" s="3">
-        <v>200</v>
       </c>
       <c r="V57" s="3">
         <v>200</v>
       </c>
       <c r="W57" s="3">
+        <v>200</v>
+      </c>
+      <c r="X57" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y57" s="3">
         <v>300</v>
-      </c>
-      <c r="X57" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>100</v>
       </c>
       <c r="Z57" s="3">
         <v>100</v>
       </c>
       <c r="AA57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC57" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AD57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE57" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG57" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F58" s="3">
         <v>1600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>4700</v>
-      </c>
-      <c r="G58" s="3">
-        <v>5000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>5100</v>
       </c>
       <c r="I58" s="3">
         <v>2500</v>
       </c>
       <c r="J58" s="3">
+        <v>5100</v>
+      </c>
+      <c r="K58" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L58" s="3">
         <v>3600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4720,11 +4987,11 @@
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -4735,8 +5002,8 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>4</v>
+      <c r="Y58" s="3">
+        <v>0</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -4744,8 +5011,8 @@
       <c r="AA58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>4</v>
+      <c r="AB58" s="3">
+        <v>0</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>4</v>
@@ -4756,16 +5023,22 @@
       <c r="AE58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
+      <c r="E59" s="3">
+        <v>300</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>4</v>
@@ -4773,18 +5046,18 @@
       <c r="G59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J59" s="3">
         <v>100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>300</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4794,222 +5067,234 @@
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>300</v>
-      </c>
-      <c r="R59" s="3">
-        <v>200</v>
-      </c>
-      <c r="S59" s="3">
-        <v>100</v>
       </c>
       <c r="T59" s="3">
         <v>200</v>
       </c>
       <c r="U59" s="3">
+        <v>100</v>
+      </c>
+      <c r="V59" s="3">
         <v>200</v>
       </c>
-      <c r="V59" s="3">
-        <v>300</v>
-      </c>
       <c r="W59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X59" s="3">
         <v>300</v>
       </c>
       <c r="Y59" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA59" s="3">
         <v>1200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>2800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F60" s="3">
         <v>3200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>8700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1400</v>
-      </c>
-      <c r="N60" s="3">
-        <v>700</v>
-      </c>
-      <c r="O60" s="3">
-        <v>900</v>
       </c>
       <c r="P60" s="3">
         <v>700</v>
       </c>
       <c r="Q60" s="3">
+        <v>900</v>
+      </c>
+      <c r="R60" s="3">
+        <v>700</v>
+      </c>
+      <c r="S60" s="3">
         <v>1400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>500</v>
-      </c>
-      <c r="S60" s="3">
-        <v>400</v>
-      </c>
-      <c r="T60" s="3">
-        <v>400</v>
       </c>
       <c r="U60" s="3">
         <v>400</v>
       </c>
       <c r="V60" s="3">
+        <v>400</v>
+      </c>
+      <c r="W60" s="3">
+        <v>400</v>
+      </c>
+      <c r="X60" s="3">
         <v>500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>200</v>
+      </c>
+      <c r="F61" s="3">
         <v>3300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>16000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>15200</v>
       </c>
-      <c r="G61" s="3">
-        <v>15300</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>200</v>
+      </c>
+      <c r="J61" s="3">
         <v>16200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>18900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>8500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>8400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>7900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>6400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>5900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>3500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1500</v>
-      </c>
-      <c r="T61" s="3">
-        <v>200</v>
-      </c>
-      <c r="U61" s="3">
-        <v>200</v>
       </c>
       <c r="V61" s="3">
         <v>200</v>
       </c>
       <c r="W61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Y61" s="3">
         <v>300</v>
       </c>
       <c r="Z61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AA61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AB61" s="3">
         <v>0</v>
@@ -5023,8 +5308,14 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5043,8 +5334,8 @@
       <c r="H62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
+      <c r="I62" s="3">
+        <v>15100</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
@@ -5061,11 +5352,11 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
-        <v>1300</v>
-      </c>
-      <c r="P62" s="3">
-        <v>1300</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q62" s="3">
         <v>1300</v>
@@ -5074,10 +5365,10 @@
         <v>1300</v>
       </c>
       <c r="S62" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="T62" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="U62" s="3">
         <v>1400</v>
@@ -5089,13 +5380,13 @@
         <v>1400</v>
       </c>
       <c r="X62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>4</v>
+        <v>1400</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>4</v>
@@ -5103,17 +5394,23 @@
       <c r="AB62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,97 +5688,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F66" s="3">
         <v>6500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>21400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>21900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>22700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>24800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>25200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>15000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>14200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>10600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>7800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>6700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>6100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>5600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>5500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>3400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>3300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>2000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>2300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>142200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>142100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>141400</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +6103,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,97 +6198,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-105600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-103100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-80100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-69200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-65000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-62400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-58300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-54900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-58200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-58700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-60100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-60400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-57100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-55700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-48900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-47200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-45100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-43600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-40600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-39000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-37500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-36700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-35800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-33300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-34000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-31400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-27700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-36800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-36200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,97 +6578,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F76" s="3">
         <v>19100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>28600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>30800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>32000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>32800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>35000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>12900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>7300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>2400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>9300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>10400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>9400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>10800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>12700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>13400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>12100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>10100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>2000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>3300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>5700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>11400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6768,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="3">
         <v>-10900</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-2600</v>
       </c>
       <c r="G81" s="3">
         <v>-4200</v>
       </c>
       <c r="H81" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" s="3">
         <v>-3400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-3300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-6800</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-2100</v>
       </c>
       <c r="R81" s="3">
         <v>-1600</v>
       </c>
       <c r="S81" s="3">
-        <v>-2900</v>
+        <v>-2100</v>
       </c>
       <c r="T81" s="3">
         <v>-1600</v>
       </c>
       <c r="U81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V81" s="3">
         <v>-1600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="X81" s="3">
         <v>-800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>11200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,31 +7002,33 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>300</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
         <v>600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
@@ -6667,10 +7064,10 @@
         <v>100</v>
       </c>
       <c r="V83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -6696,8 +7093,14 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,97 +7568,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="3">
         <v>-800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2000</v>
       </c>
-      <c r="G89" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3">
         <v>-5200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1300</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-900</v>
       </c>
       <c r="M89" s="3">
         <v>-1500</v>
       </c>
       <c r="N89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="O89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="P89" s="3">
         <v>-1000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-800</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-1200</v>
       </c>
       <c r="T89" s="3">
         <v>-1500</v>
       </c>
       <c r="U89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="V89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="W89" s="3">
         <v>-1600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-1200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-300</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-7600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,85 +7702,87 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3">
         <v>200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3">
         <v>-2200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-2000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-100</v>
-      </c>
       <c r="T91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="U91" s="3">
         <v>-100</v>
       </c>
       <c r="V91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X91" s="3">
         <v>-700</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -7349,11 +7790,17 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,97 +7983,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3">
         <v>200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3">
         <v>-2200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-2000</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>2100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>1000</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>6000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>100</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +8117,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7690,11 +8157,11 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7741,8 +8208,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,13 +8493,19 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>4</v>
+      <c r="D100" s="3">
+        <v>2500</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>4</v>
@@ -8022,83 +8513,89 @@
       <c r="F100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G100" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>11400</v>
-      </c>
-      <c r="J100" s="3">
-        <v>3700</v>
-      </c>
-      <c r="K100" s="3">
-        <v>2800</v>
       </c>
       <c r="L100" s="3">
         <v>3700</v>
       </c>
       <c r="M100" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N100" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O100" s="3">
         <v>1600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U100" s="3">
         <v>2100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>2500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>2500</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>300</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>1400</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8135,11 +8632,11 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8186,93 +8683,105 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2100</v>
       </c>
-      <c r="G102" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-7400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>7600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>4400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>1200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>1500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-100</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-600</v>
       </c>
     </row>
